--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900329</v>
+        <v>128900371</v>
       </c>
       <c r="B15" t="n">
-        <v>91808</v>
+        <v>83011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,37 +2066,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602681</v>
+        <v>602623</v>
       </c>
       <c r="R15" t="n">
-        <v>6979457</v>
+        <v>6979560</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2134,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2156,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128900366</v>
+        <v>128900329</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>91808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,34 +2163,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>73</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602670</v>
+        <v>602681</v>
       </c>
       <c r="R16" t="n">
-        <v>6979642</v>
+        <v>6979457</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,6 +2234,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900371</v>
+        <v>128900366</v>
       </c>
       <c r="B17" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602623</v>
+        <v>602670</v>
       </c>
       <c r="R17" t="n">
-        <v>6979560</v>
+        <v>6979642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B18" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,37 +2361,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R18" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,24 +2429,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2466,10 +2447,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900348</v>
+        <v>128900325</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>91808</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,34 +2458,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>73</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602903</v>
+        <v>602673</v>
       </c>
       <c r="R19" t="n">
-        <v>6979432</v>
+        <v>6979482</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,8 +2529,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B21" t="n">
-        <v>91808</v>
+        <v>91544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,37 +2671,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R21" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,24 +2739,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2776,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B22" t="n">
-        <v>91544</v>
+        <v>91808</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,34 +2768,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R22" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,8 +2839,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3164,32 +3164,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900346</v>
+        <v>128900339</v>
       </c>
       <c r="B26" t="n">
-        <v>91510</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4660</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602871</v>
+        <v>602837</v>
       </c>
       <c r="R26" t="n">
-        <v>6979361</v>
+        <v>6979499</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3358,32 +3358,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900339</v>
+        <v>128900346</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>91510</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602837</v>
+        <v>602871</v>
       </c>
       <c r="R28" t="n">
-        <v>6979499</v>
+        <v>6979361</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>128900358</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>128900352</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>128900331</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>128900341</v>
       </c>
       <c r="B8" t="n">
-        <v>91537</v>
+        <v>91544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,56 +1440,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B9" t="n">
-        <v>91804</v>
+        <v>83015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R9" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,29 +1519,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,45 +1537,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B10" t="n">
-        <v>83011</v>
+        <v>91811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R10" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,8 +1627,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1669,7 +1669,7 @@
         <v>128900373</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900354</v>
+        <v>128900364</v>
       </c>
       <c r="B12" t="n">
-        <v>82898</v>
+        <v>83015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602883</v>
+        <v>602698</v>
       </c>
       <c r="R12" t="n">
-        <v>6979584</v>
+        <v>6979648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>128900335</v>
       </c>
       <c r="B13" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900364</v>
+        <v>128900354</v>
       </c>
       <c r="B14" t="n">
-        <v>83011</v>
+        <v>82902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602698</v>
+        <v>602883</v>
       </c>
       <c r="R14" t="n">
-        <v>6979648</v>
+        <v>6979584</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,6 +2036,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900371</v>
+        <v>128900329</v>
       </c>
       <c r="B15" t="n">
-        <v>83011</v>
+        <v>91815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,34 +2066,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>73</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602623</v>
+        <v>602681</v>
       </c>
       <c r="R15" t="n">
-        <v>6979560</v>
+        <v>6979457</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,6 +2137,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128900329</v>
+        <v>128900371</v>
       </c>
       <c r="B16" t="n">
-        <v>91808</v>
+        <v>83015</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,37 +2167,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602681</v>
+        <v>602623</v>
       </c>
       <c r="R16" t="n">
-        <v>6979457</v>
+        <v>6979560</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,7 +2235,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>128900366</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>79658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R18" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>128900325</v>
       </c>
       <c r="B19" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900362</v>
+        <v>128900348</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>91533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602738</v>
+        <v>602903</v>
       </c>
       <c r="R20" t="n">
-        <v>6979736</v>
+        <v>6979432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B21" t="n">
-        <v>91544</v>
+        <v>91815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,34 +2671,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R21" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,8 +2742,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2757,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B22" t="n">
-        <v>91808</v>
+        <v>91551</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,37 +2787,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R22" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2839,24 +2855,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2876,7 +2876,7 @@
         <v>128900350</v>
       </c>
       <c r="B23" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128900356</v>
       </c>
       <c r="B24" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128900344</v>
       </c>
       <c r="B25" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3164,32 +3164,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900339</v>
+        <v>128900346</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>91517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602837</v>
+        <v>602871</v>
       </c>
       <c r="R26" t="n">
-        <v>6979499</v>
+        <v>6979361</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128900360</v>
+        <v>128900339</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3272,21 +3272,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602724</v>
+        <v>602837</v>
       </c>
       <c r="R27" t="n">
-        <v>6979757</v>
+        <v>6979499</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,32 +3358,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900346</v>
+        <v>128900360</v>
       </c>
       <c r="B28" t="n">
-        <v>91510</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602871</v>
+        <v>602724</v>
       </c>
       <c r="R28" t="n">
-        <v>6979361</v>
+        <v>6979757</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>128900341</v>
       </c>
       <c r="B8" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,45 +1440,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B9" t="n">
-        <v>83015</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R9" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,8 +1530,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1537,56 +1569,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B10" t="n">
-        <v>91811</v>
+        <v>83005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R10" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,29 +1648,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1766,7 +1766,7 @@
         <v>128900364</v>
       </c>
       <c r="B12" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>128900354</v>
       </c>
       <c r="B14" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900329</v>
+        <v>128900366</v>
       </c>
       <c r="B15" t="n">
-        <v>91815</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,37 +2066,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602681</v>
+        <v>602670</v>
       </c>
       <c r="R15" t="n">
-        <v>6979457</v>
+        <v>6979642</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2134,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2159,7 +2155,7 @@
         <v>128900371</v>
       </c>
       <c r="B16" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900366</v>
+        <v>128900329</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>91822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2264,34 +2260,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>73</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602670</v>
+        <v>602681</v>
       </c>
       <c r="R17" t="n">
-        <v>6979642</v>
+        <v>6979457</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,6 +2331,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900362</v>
+        <v>128900325</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>91822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,34 +2361,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>73</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602738</v>
+        <v>602673</v>
       </c>
       <c r="R18" t="n">
-        <v>6979736</v>
+        <v>6979482</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,8 +2432,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2447,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B19" t="n">
-        <v>91815</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,37 +2477,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R19" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,24 +2545,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2563,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B20" t="n">
-        <v>91533</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R20" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
         <v>128900321</v>
       </c>
       <c r="B21" t="n">
-        <v>91815</v>
+        <v>91822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128900343</v>
       </c>
       <c r="B22" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>128900350</v>
       </c>
       <c r="B23" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128900356</v>
       </c>
       <c r="B24" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128900344</v>
       </c>
       <c r="B25" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3164,32 +3164,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900346</v>
+        <v>128900360</v>
       </c>
       <c r="B26" t="n">
-        <v>91517</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602871</v>
+        <v>602724</v>
       </c>
       <c r="R26" t="n">
-        <v>6979361</v>
+        <v>6979757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3358,32 +3358,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900360</v>
+        <v>128900346</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>91524</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602724</v>
+        <v>602871</v>
       </c>
       <c r="R28" t="n">
-        <v>6979757</v>
+        <v>6979361</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>128900358</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>128900352</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>128900331</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>128900341</v>
       </c>
       <c r="B8" t="n">
-        <v>91551</v>
+        <v>91553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,56 +1440,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>83007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R9" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,29 +1519,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,45 +1537,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B10" t="n">
-        <v>83005</v>
+        <v>91820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R10" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,8 +1627,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1669,7 +1669,7 @@
         <v>128900373</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900364</v>
+        <v>128900354</v>
       </c>
       <c r="B12" t="n">
-        <v>83005</v>
+        <v>82873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602698</v>
+        <v>602883</v>
       </c>
       <c r="R12" t="n">
-        <v>6979648</v>
+        <v>6979584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,6 +1842,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1860,32 +1861,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900335</v>
+        <v>128900364</v>
       </c>
       <c r="B13" t="n">
-        <v>80179</v>
+        <v>83007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602837</v>
+        <v>602698</v>
       </c>
       <c r="R13" t="n">
-        <v>6979499</v>
+        <v>6979648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,32 +1958,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900354</v>
+        <v>128900335</v>
       </c>
       <c r="B14" t="n">
-        <v>82871</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602883</v>
+        <v>602837</v>
       </c>
       <c r="R14" t="n">
-        <v>6979584</v>
+        <v>6979499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2037,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>128900366</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>128900371</v>
       </c>
       <c r="B16" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128900329</v>
       </c>
       <c r="B17" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B18" t="n">
-        <v>91822</v>
+        <v>91542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,37 +2361,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R18" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,24 +2429,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2466,10 +2447,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>79660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,21 +2458,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2501,10 +2482,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R19" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900362</v>
+        <v>128900325</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>91824</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,34 +2555,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>73</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602738</v>
+        <v>602673</v>
       </c>
       <c r="R20" t="n">
-        <v>6979736</v>
+        <v>6979482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,8 +2626,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B21" t="n">
-        <v>91822</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,37 +2671,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R21" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,24 +2739,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2776,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B22" t="n">
-        <v>91558</v>
+        <v>91824</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,34 +2768,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R22" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,8 +2839,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2876,7 +2876,7 @@
         <v>128900350</v>
       </c>
       <c r="B23" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128900356</v>
       </c>
       <c r="B24" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>128900344</v>
       </c>
       <c r="B25" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3164,32 +3164,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900360</v>
+        <v>128900346</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>91526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602724</v>
+        <v>602871</v>
       </c>
       <c r="R26" t="n">
-        <v>6979757</v>
+        <v>6979361</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,7 +3264,7 @@
         <v>128900339</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,32 +3358,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900346</v>
+        <v>128900360</v>
       </c>
       <c r="B28" t="n">
-        <v>91524</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602871</v>
+        <v>602724</v>
       </c>
       <c r="R28" t="n">
-        <v>6979361</v>
+        <v>6979757</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1440,45 +1440,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B9" t="n">
-        <v>83007</v>
+        <v>91820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R9" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,8 +1530,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1537,56 +1569,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B10" t="n">
-        <v>91820</v>
+        <v>83007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R10" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,29 +1648,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1861,32 +1861,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900364</v>
+        <v>128900335</v>
       </c>
       <c r="B13" t="n">
-        <v>83007</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602698</v>
+        <v>602837</v>
       </c>
       <c r="R13" t="n">
-        <v>6979648</v>
+        <v>6979499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,32 +1958,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900335</v>
+        <v>128900364</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>83007</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602837</v>
+        <v>602698</v>
       </c>
       <c r="R14" t="n">
-        <v>6979499</v>
+        <v>6979648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900366</v>
+        <v>128900329</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>91824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,34 +2066,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>73</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602670</v>
+        <v>602681</v>
       </c>
       <c r="R15" t="n">
-        <v>6979642</v>
+        <v>6979457</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,6 +2137,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2152,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128900371</v>
+        <v>128900366</v>
       </c>
       <c r="B16" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,21 +2167,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2191,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602623</v>
+        <v>602670</v>
       </c>
       <c r="R16" t="n">
-        <v>6979560</v>
+        <v>6979642</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,10 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900329</v>
+        <v>128900371</v>
       </c>
       <c r="B17" t="n">
-        <v>91824</v>
+        <v>83007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,37 +2264,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602681</v>
+        <v>602623</v>
       </c>
       <c r="R17" t="n">
-        <v>6979457</v>
+        <v>6979560</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,7 +2332,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B18" t="n">
-        <v>91542</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R18" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900362</v>
+        <v>128900325</v>
       </c>
       <c r="B19" t="n">
-        <v>79660</v>
+        <v>91824</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,34 +2458,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>73</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602738</v>
+        <v>602673</v>
       </c>
       <c r="R19" t="n">
-        <v>6979736</v>
+        <v>6979482</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,8 +2529,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2544,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B20" t="n">
-        <v>91824</v>
+        <v>91542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,37 +2574,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R20" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,24 +2642,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>91824</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,34 +2671,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R21" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,8 +2742,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2757,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B22" t="n">
-        <v>91824</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,37 +2787,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R22" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2839,24 +2855,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900362</v>
+        <v>128900348</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>91542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602738</v>
+        <v>602903</v>
       </c>
       <c r="R18" t="n">
-        <v>6979736</v>
+        <v>6979432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B20" t="n">
-        <v>91542</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R20" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>128900341</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>91551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,56 +1440,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B9" t="n">
-        <v>91820</v>
+        <v>83007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R9" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,29 +1519,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,45 +1537,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B10" t="n">
-        <v>83007</v>
+        <v>91830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R10" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,8 +1627,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900354</v>
+        <v>128900364</v>
       </c>
       <c r="B12" t="n">
-        <v>82873</v>
+        <v>83007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602883</v>
+        <v>602698</v>
       </c>
       <c r="R12" t="n">
-        <v>6979584</v>
+        <v>6979648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1861,32 +1860,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900335</v>
+        <v>128900354</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>82873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602837</v>
+        <v>602883</v>
       </c>
       <c r="R13" t="n">
-        <v>6979499</v>
+        <v>6979584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,6 +1939,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1958,32 +1958,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900364</v>
+        <v>128900335</v>
       </c>
       <c r="B14" t="n">
-        <v>83007</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602698</v>
+        <v>602837</v>
       </c>
       <c r="R14" t="n">
-        <v>6979648</v>
+        <v>6979499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
         <v>128900329</v>
       </c>
       <c r="B15" t="n">
-        <v>91824</v>
+        <v>91834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B18" t="n">
-        <v>91542</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R18" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B19" t="n">
-        <v>91824</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,37 +2458,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R19" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,24 +2526,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2563,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900362</v>
+        <v>128900325</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>91834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,34 +2555,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>73</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602738</v>
+        <v>602673</v>
       </c>
       <c r="R20" t="n">
-        <v>6979736</v>
+        <v>6979482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,8 +2626,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B21" t="n">
-        <v>91824</v>
+        <v>91558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,37 +2671,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R21" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,24 +2739,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2776,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,34 +2768,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R22" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,8 +2839,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2876,7 +2876,7 @@
         <v>128900350</v>
       </c>
       <c r="B23" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>128900356</v>
       </c>
       <c r="B24" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>128900346</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>91524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128900339</v>
+        <v>128900360</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3272,21 +3272,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602837</v>
+        <v>602724</v>
       </c>
       <c r="R27" t="n">
-        <v>6979499</v>
+        <v>6979757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900360</v>
+        <v>128900339</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,21 +3369,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602724</v>
+        <v>602837</v>
       </c>
       <c r="R28" t="n">
-        <v>6979757</v>
+        <v>6979499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1440,45 +1440,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B9" t="n">
-        <v>83007</v>
+        <v>91831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R9" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,8 +1530,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1537,56 +1569,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B10" t="n">
-        <v>91830</v>
+        <v>83007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R10" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,29 +1648,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2058,7 +2058,7 @@
         <v>128900329</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900362</v>
+        <v>128900325</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>91835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,34 +2361,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>73</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602738</v>
+        <v>602673</v>
       </c>
       <c r="R18" t="n">
-        <v>6979736</v>
+        <v>6979482</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,8 +2432,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2447,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>79660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,21 +2477,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2482,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R19" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>91540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,37 +2574,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R20" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,24 +2642,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B21" t="n">
-        <v>91558</v>
+        <v>91835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,34 +2671,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R21" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,8 +2742,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2757,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,37 +2787,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R22" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2839,24 +2851,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2973,7 +2969,7 @@
         <v>128900356</v>
       </c>
       <c r="B24" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,32 +3160,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900346</v>
+        <v>128900360</v>
       </c>
       <c r="B26" t="n">
-        <v>91524</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602871</v>
+        <v>602724</v>
       </c>
       <c r="R26" t="n">
-        <v>6979361</v>
+        <v>6979757</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,10 +3257,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128900360</v>
+        <v>128900339</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3272,21 +3268,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3296,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602724</v>
+        <v>602837</v>
       </c>
       <c r="R27" t="n">
-        <v>6979757</v>
+        <v>6979499</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,32 +3354,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900339</v>
+        <v>128900346</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>91524</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3393,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602837</v>
+        <v>602871</v>
       </c>
       <c r="R28" t="n">
-        <v>6979499</v>
+        <v>6979361</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1860,32 +1860,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900354</v>
+        <v>128900335</v>
       </c>
       <c r="B13" t="n">
-        <v>82873</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602883</v>
+        <v>602837</v>
       </c>
       <c r="R13" t="n">
-        <v>6979584</v>
+        <v>6979499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1939,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1958,32 +1957,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900335</v>
+        <v>128900354</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>82873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602837</v>
+        <v>602883</v>
       </c>
       <c r="R14" t="n">
-        <v>6979499</v>
+        <v>6979584</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,6 +2036,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900362</v>
+        <v>128900348</v>
       </c>
       <c r="B19" t="n">
-        <v>79660</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,21 +2477,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602738</v>
+        <v>602903</v>
       </c>
       <c r="R19" t="n">
-        <v>6979736</v>
+        <v>6979432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900348</v>
+        <v>128900362</v>
       </c>
       <c r="B20" t="n">
-        <v>91540</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602903</v>
+        <v>602738</v>
       </c>
       <c r="R20" t="n">
-        <v>6979432</v>
+        <v>6979736</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B21" t="n">
-        <v>91835</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,37 +2671,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R21" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,24 +2735,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2776,10 +2753,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>91835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,30 +2764,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Fomitopsis pulvinascens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R22" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,8 +2835,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3160,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900360</v>
+        <v>128900339</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602724</v>
+        <v>602837</v>
       </c>
       <c r="R26" t="n">
-        <v>6979757</v>
+        <v>6979499</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128900339</v>
+        <v>128900360</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602837</v>
+        <v>602724</v>
       </c>
       <c r="R27" t="n">
-        <v>6979499</v>
+        <v>6979757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>128900358</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>128900352</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>128900331</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>128900341</v>
       </c>
       <c r="B8" t="n">
-        <v>91551</v>
+        <v>91554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,56 +1440,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B9" t="n">
-        <v>91831</v>
+        <v>83011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R9" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,29 +1519,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1569,45 +1537,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B10" t="n">
-        <v>83007</v>
+        <v>91834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R10" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,8 +1627,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1669,7 +1669,7 @@
         <v>128900373</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900364</v>
+        <v>128900354</v>
       </c>
       <c r="B12" t="n">
-        <v>83007</v>
+        <v>82877</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602698</v>
+        <v>602883</v>
       </c>
       <c r="R12" t="n">
-        <v>6979648</v>
+        <v>6979584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,6 +1842,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1860,32 +1861,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900335</v>
+        <v>128900364</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>83011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602837</v>
+        <v>602698</v>
       </c>
       <c r="R13" t="n">
-        <v>6979499</v>
+        <v>6979648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,32 +1958,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900354</v>
+        <v>128900335</v>
       </c>
       <c r="B14" t="n">
-        <v>82873</v>
+        <v>80183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602883</v>
+        <v>602837</v>
       </c>
       <c r="R14" t="n">
-        <v>6979584</v>
+        <v>6979499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2037,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900329</v>
+        <v>128900366</v>
       </c>
       <c r="B15" t="n">
-        <v>91835</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,37 +2066,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602681</v>
+        <v>602670</v>
       </c>
       <c r="R15" t="n">
-        <v>6979457</v>
+        <v>6979642</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2134,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2156,10 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128900366</v>
+        <v>128900371</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>83011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,21 +2163,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2191,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602670</v>
+        <v>602623</v>
       </c>
       <c r="R16" t="n">
-        <v>6979642</v>
+        <v>6979560</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900371</v>
+        <v>128900329</v>
       </c>
       <c r="B17" t="n">
-        <v>83007</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2264,34 +2260,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>73</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602623</v>
+        <v>602681</v>
       </c>
       <c r="R17" t="n">
-        <v>6979560</v>
+        <v>6979457</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,6 +2331,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>128900325</v>
       </c>
       <c r="B18" t="n">
-        <v>91835</v>
+        <v>91838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>128900348</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128900362</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900343</v>
+        <v>128900321</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,30 +2671,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Fomitopsis pulvinascens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602836</v>
+        <v>602666</v>
       </c>
       <c r="R21" t="n">
-        <v>6979368</v>
+        <v>6979501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,8 +2742,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2753,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900321</v>
+        <v>128900343</v>
       </c>
       <c r="B22" t="n">
-        <v>91835</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2764,37 +2787,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602666</v>
+        <v>602836</v>
       </c>
       <c r="R22" t="n">
-        <v>6979501</v>
+        <v>6979368</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,24 +2851,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2872,7 +2872,7 @@
         <v>128900350</v>
       </c>
       <c r="B23" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128900356</v>
       </c>
       <c r="B24" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128900344</v>
       </c>
       <c r="B25" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>128900339</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128900360</v>
+        <v>128900346</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>91527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602724</v>
+        <v>602871</v>
       </c>
       <c r="R27" t="n">
-        <v>6979757</v>
+        <v>6979361</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,32 +3354,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900346</v>
+        <v>128900360</v>
       </c>
       <c r="B28" t="n">
-        <v>91524</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602871</v>
+        <v>602724</v>
       </c>
       <c r="R28" t="n">
-        <v>6979361</v>
+        <v>6979757</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B18" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,37 +2361,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R18" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,24 +2429,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2466,10 +2447,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900348</v>
+        <v>128900325</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,34 +2458,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>73</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602903</v>
+        <v>602673</v>
       </c>
       <c r="R19" t="n">
-        <v>6979432</v>
+        <v>6979482</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,8 +2529,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>128900358</v>
       </c>
       <c r="B5" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>128900352</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>128900331</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>128900341</v>
       </c>
       <c r="B8" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,45 +1440,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900369</v>
+        <v>128900327</v>
       </c>
       <c r="B9" t="n">
-        <v>83011</v>
+        <v>91836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602622</v>
+        <v>602681</v>
       </c>
       <c r="R9" t="n">
-        <v>6979655</v>
+        <v>6979457</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,8 +1530,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1537,56 +1569,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900327</v>
+        <v>128900369</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>83012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1964</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602681</v>
+        <v>602622</v>
       </c>
       <c r="R10" t="n">
-        <v>6979457</v>
+        <v>6979655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,29 +1648,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1669,7 +1669,7 @@
         <v>128900373</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>128900354</v>
       </c>
       <c r="B12" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>128900364</v>
       </c>
       <c r="B13" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>128900335</v>
       </c>
       <c r="B14" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>128900366</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>128900371</v>
       </c>
       <c r="B16" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>128900329</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900348</v>
+        <v>128900325</v>
       </c>
       <c r="B18" t="n">
-        <v>91543</v>
+        <v>91840</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,34 +2361,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>73</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602903</v>
+        <v>602673</v>
       </c>
       <c r="R18" t="n">
-        <v>6979432</v>
+        <v>6979482</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,8 +2432,24 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2447,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900325</v>
+        <v>128900348</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>91545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,37 +2477,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>73</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602673</v>
+        <v>602903</v>
       </c>
       <c r="R19" t="n">
-        <v>6979482</v>
+        <v>6979432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,24 +2545,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2566,7 +2566,7 @@
         <v>128900362</v>
       </c>
       <c r="B20" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>128900321</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
+        <v>91840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>128900343</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>128900350</v>
       </c>
       <c r="B23" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>128900356</v>
       </c>
       <c r="B24" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>128900344</v>
       </c>
       <c r="B25" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900339</v>
+        <v>128900346</v>
       </c>
       <c r="B26" t="n">
-        <v>80148</v>
+        <v>91529</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602837</v>
+        <v>602871</v>
       </c>
       <c r="R26" t="n">
-        <v>6979499</v>
+        <v>6979361</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128900346</v>
+        <v>128900360</v>
       </c>
       <c r="B27" t="n">
-        <v>91527</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602871</v>
+        <v>602724</v>
       </c>
       <c r="R27" t="n">
-        <v>6979361</v>
+        <v>6979757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900360</v>
+        <v>128900339</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602724</v>
+        <v>602837</v>
       </c>
       <c r="R28" t="n">
-        <v>6979757</v>
+        <v>6979499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3449,6 +3449,4626 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129627765</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>602904</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6979415</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall färska spår.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129627686</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>602797</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6979572</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129627764</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>602916</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6979371</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129627689</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>602773</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6979714</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129627771</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>602782</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6979624</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129627690</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>602770</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6979694</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129627774</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>602748</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6979628</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129627685</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>602797</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6979575</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129627762</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>602818</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6979362</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129627687</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>602794</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6979575</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129627684</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>602714</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6979668</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129627780</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>602750</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6979588</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129627691</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>602779</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6979669</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129627667</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>602690</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6979583</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129627779</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>602869</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6979601</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129627671</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>602903</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6979431</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129627692</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>602707</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6979618</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129627674</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>602809</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6979547</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129627669</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>602791</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6979625</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sannolikt ett påbörjat bohål av vad som kan vara tretåig hackspett. Sitter 2 meter ovan mark i en asp. Bohålet är inte klart, men öppningen mättes till omkring 4 centimeter.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129627778</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>602935</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6979389</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129627695</v>
+      </c>
+      <c r="B49" t="n">
+        <v>88952</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>510</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>602860</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6979447</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129627688</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>602759</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6979557</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129627768</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>602780</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6979618</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, färska spår på tall.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129627666</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>602670</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6979481</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129627677</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>602776</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6979680</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129627694</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91567</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>602905</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6979425</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129627775</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>602854</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6979675</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129627693</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>602722</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6979623</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129627772</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>602908</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6979328</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129627766</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>602935</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6979466</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129627673</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>602857</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6979536</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129627773</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>602909</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6979335</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129627678</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>602750</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6979758</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129627672</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>602872</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6979492</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129627670</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>602850</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6979445</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129627681</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>602787</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6979696</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129627763</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>602896</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6979327</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129627767</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>602703</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6979746</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129627777</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>602720</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6979669</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>150 stycken ca</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129627770</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>602876</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6979597</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2 ex, övriga/lockläten läten.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129627680</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>602732</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6979746</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129627675</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>602835</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6979550</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129627682</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>602720</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6979665</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129627769</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>602761</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6979565</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129627679</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>602740</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6979774</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129627676</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kroktjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>602825</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6979660</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3553,10 +3553,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627686</v>
+        <v>129627689</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602797</v>
+        <v>602773</v>
       </c>
       <c r="R30" t="n">
-        <v>6979572</v>
+        <v>6979714</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627764</v>
+        <v>129627686</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602916</v>
+        <v>602797</v>
       </c>
       <c r="R31" t="n">
-        <v>6979371</v>
+        <v>6979572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627689</v>
+        <v>129627764</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3768,16 +3768,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602773</v>
+        <v>602916</v>
       </c>
       <c r="R32" t="n">
-        <v>6979714</v>
+        <v>6979371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3956,32 +3956,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627690</v>
+        <v>129627685</v>
       </c>
       <c r="B34" t="n">
-        <v>97598</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602770</v>
+        <v>602797</v>
       </c>
       <c r="R34" t="n">
-        <v>6979694</v>
+        <v>6979575</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,6 +4027,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4150,32 +4155,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627685</v>
+        <v>129627690</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>97598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4190,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602797</v>
+        <v>602770</v>
       </c>
       <c r="R36" t="n">
-        <v>6979575</v>
+        <v>6979694</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4221,11 +4226,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4946,10 +4946,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627671</v>
+        <v>129627692</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4957,21 +4957,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602903</v>
+        <v>602707</v>
       </c>
       <c r="R44" t="n">
-        <v>6979431</v>
+        <v>6979618</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5017,11 +5017,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,10 +5043,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129627692</v>
+        <v>129627671</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,21 +5054,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5078,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>602707</v>
+        <v>602903</v>
       </c>
       <c r="R45" t="n">
-        <v>6979618</v>
+        <v>6979431</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5119,6 +5114,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129627669</v>
+        <v>129627778</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5258,42 +5258,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>602791</v>
+        <v>602935</v>
       </c>
       <c r="R47" t="n">
-        <v>6979625</v>
+        <v>6979389</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5326,11 +5318,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sannolikt ett påbörjat bohål av vad som kan vara tretåig hackspett. Sitter 2 meter ovan mark i en asp. Bohålet är inte klart, men öppningen mättes till omkring 4 centimeter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5357,10 +5344,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129627778</v>
+        <v>129627669</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5368,34 +5355,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>602935</v>
+        <v>602791</v>
       </c>
       <c r="R48" t="n">
-        <v>6979389</v>
+        <v>6979625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5428,6 +5423,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sannolikt ett påbörjat bohål av vad som kan vara tretåig hackspett. Sitter 2 meter ovan mark i en asp. Bohålet är inte klart, men öppningen mättes till omkring 4 centimeter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6342,10 +6342,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129627766</v>
+        <v>129627773</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6353,21 +6353,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602935</v>
+        <v>602909</v>
       </c>
       <c r="R58" t="n">
-        <v>6979466</v>
+        <v>6979335</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6413,11 +6413,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6444,7 +6439,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129627673</v>
+        <v>129627766</v>
       </c>
       <c r="B59" t="n">
         <v>57727</v>
@@ -6479,10 +6474,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602857</v>
+        <v>602935</v>
       </c>
       <c r="R59" t="n">
-        <v>6979536</v>
+        <v>6979466</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6519,7 +6514,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6546,10 +6541,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129627773</v>
+        <v>129627673</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6557,21 +6552,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6581,10 +6576,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602909</v>
+        <v>602857</v>
       </c>
       <c r="R60" t="n">
-        <v>6979335</v>
+        <v>6979536</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6617,6 +6612,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7153,32 +7153,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627767</v>
+        <v>129627777</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602703</v>
+        <v>602720</v>
       </c>
       <c r="R66" t="n">
-        <v>6979746</v>
+        <v>6979669</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>150 stycken ca</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7255,32 +7255,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129627777</v>
+        <v>129627767</v>
       </c>
       <c r="B67" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602720</v>
+        <v>602703</v>
       </c>
       <c r="R67" t="n">
-        <v>6979669</v>
+        <v>6979746</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>150 stycken ca</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7357,10 +7357,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627770</v>
+        <v>129627680</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7368,21 +7368,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602876</v>
+        <v>602732</v>
       </c>
       <c r="R68" t="n">
-        <v>6979597</v>
+        <v>6979746</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>2 ex, övriga/lockläten läten.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7459,7 +7459,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627680</v>
+        <v>129627675</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602732</v>
+        <v>602835</v>
       </c>
       <c r="R69" t="n">
-        <v>6979746</v>
+        <v>6979550</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627675</v>
+        <v>129627682</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602835</v>
+        <v>602720</v>
       </c>
       <c r="R70" t="n">
-        <v>6979550</v>
+        <v>6979665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7663,10 +7663,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129627682</v>
+        <v>129627770</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7674,21 +7674,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602720</v>
+        <v>602876</v>
       </c>
       <c r="R71" t="n">
-        <v>6979665</v>
+        <v>6979597</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 ex, övriga/lockläten läten.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3655,7 +3655,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627686</v>
+        <v>129627764</v>
       </c>
       <c r="B31" t="n">
         <v>57727</v>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602797</v>
+        <v>602916</v>
       </c>
       <c r="R31" t="n">
-        <v>6979572</v>
+        <v>6979371</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3757,7 +3757,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627764</v>
+        <v>129627686</v>
       </c>
       <c r="B32" t="n">
         <v>57727</v>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602916</v>
+        <v>602797</v>
       </c>
       <c r="R32" t="n">
-        <v>6979371</v>
+        <v>6979572</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3956,10 +3956,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627685</v>
+        <v>129627774</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,21 +3967,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602797</v>
+        <v>602748</v>
       </c>
       <c r="R34" t="n">
-        <v>6979575</v>
+        <v>6979628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,11 +4027,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4058,10 +4053,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627774</v>
+        <v>129627685</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4069,21 +4064,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4093,10 +4088,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602748</v>
+        <v>602797</v>
       </c>
       <c r="R35" t="n">
-        <v>6979628</v>
+        <v>6979575</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4129,6 +4124,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4252,7 +4252,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627762</v>
+        <v>129627687</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602818</v>
+        <v>602794</v>
       </c>
       <c r="R37" t="n">
-        <v>6979362</v>
+        <v>6979575</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,7 +4354,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627687</v>
+        <v>129627762</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602794</v>
+        <v>602818</v>
       </c>
       <c r="R38" t="n">
-        <v>6979575</v>
+        <v>6979362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R42" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627779</v>
+        <v>129627667</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602869</v>
+        <v>602690</v>
       </c>
       <c r="R43" t="n">
-        <v>6979601</v>
+        <v>6979583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5247,10 +5247,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129627778</v>
+        <v>129627695</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>88952</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>602935</v>
+        <v>602860</v>
       </c>
       <c r="R47" t="n">
-        <v>6979389</v>
+        <v>6979447</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129627669</v>
+        <v>129627778</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5355,42 +5355,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>602791</v>
+        <v>602935</v>
       </c>
       <c r="R48" t="n">
-        <v>6979625</v>
+        <v>6979389</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5423,11 +5415,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sannolikt ett påbörjat bohål av vad som kan vara tretåig hackspett. Sitter 2 meter ovan mark i en asp. Bohålet är inte klart, men öppningen mättes till omkring 4 centimeter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5454,10 +5441,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129627695</v>
+        <v>129627688</v>
       </c>
       <c r="B49" t="n">
-        <v>88952</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5465,21 +5452,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5489,10 +5476,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>602860</v>
+        <v>602759</v>
       </c>
       <c r="R49" t="n">
-        <v>6979447</v>
+        <v>6979557</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5525,6 +5512,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5551,7 +5543,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627688</v>
+        <v>129627768</v>
       </c>
       <c r="B50" t="n">
         <v>57727</v>
@@ -5586,10 +5578,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602759</v>
+        <v>602780</v>
       </c>
       <c r="R50" t="n">
-        <v>6979557</v>
+        <v>6979618</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5626,7 +5618,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett, färska spår på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5653,32 +5645,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627768</v>
+        <v>129627666</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5688,10 +5680,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>602780</v>
+        <v>602670</v>
       </c>
       <c r="R51" t="n">
-        <v>6979618</v>
+        <v>6979481</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5724,11 +5716,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, färska spår på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5755,32 +5742,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129627666</v>
+        <v>129627677</v>
       </c>
       <c r="B52" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5790,10 +5777,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>602670</v>
+        <v>602776</v>
       </c>
       <c r="R52" t="n">
-        <v>6979481</v>
+        <v>6979680</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5826,6 +5813,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5852,10 +5844,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129627677</v>
+        <v>129627775</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5863,21 +5855,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5887,10 +5879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602776</v>
+        <v>602854</v>
       </c>
       <c r="R53" t="n">
-        <v>6979680</v>
+        <v>6979675</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5923,11 +5915,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6051,10 +6038,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129627775</v>
+        <v>129627693</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6062,21 +6049,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6086,10 +6073,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>602854</v>
+        <v>602722</v>
       </c>
       <c r="R55" t="n">
-        <v>6979675</v>
+        <v>6979623</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6148,10 +6135,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129627693</v>
+        <v>129627772</v>
       </c>
       <c r="B56" t="n">
-        <v>78801</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,21 +6146,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6183,10 +6170,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>602722</v>
+        <v>602908</v>
       </c>
       <c r="R56" t="n">
-        <v>6979623</v>
+        <v>6979328</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,7 +6232,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129627772</v>
+        <v>129627773</v>
       </c>
       <c r="B57" t="n">
         <v>80149</v>
@@ -6280,10 +6267,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>602908</v>
+        <v>602909</v>
       </c>
       <c r="R57" t="n">
-        <v>6979328</v>
+        <v>6979335</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,10 +6329,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129627773</v>
+        <v>129627672</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6353,21 +6340,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6377,10 +6364,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602909</v>
+        <v>602872</v>
       </c>
       <c r="R58" t="n">
-        <v>6979335</v>
+        <v>6979492</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6413,6 +6400,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6541,7 +6533,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129627673</v>
+        <v>129627678</v>
       </c>
       <c r="B60" t="n">
         <v>57727</v>
@@ -6576,10 +6568,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602857</v>
+        <v>602750</v>
       </c>
       <c r="R60" t="n">
-        <v>6979536</v>
+        <v>6979758</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6643,7 +6635,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129627678</v>
+        <v>129627673</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -6678,10 +6670,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602750</v>
+        <v>602857</v>
       </c>
       <c r="R61" t="n">
-        <v>6979758</v>
+        <v>6979536</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6745,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129627672</v>
+        <v>129627681</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -6780,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602872</v>
+        <v>602787</v>
       </c>
       <c r="R62" t="n">
-        <v>6979492</v>
+        <v>6979696</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6847,7 +6839,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129627670</v>
+        <v>129627763</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -6882,10 +6874,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602850</v>
+        <v>602896</v>
       </c>
       <c r="R63" t="n">
-        <v>6979445</v>
+        <v>6979327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6922,7 +6914,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6949,7 +6941,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129627681</v>
+        <v>129627670</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -6984,10 +6976,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602787</v>
+        <v>602850</v>
       </c>
       <c r="R64" t="n">
-        <v>6979696</v>
+        <v>6979445</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7051,7 +7043,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627763</v>
+        <v>129627767</v>
       </c>
       <c r="B65" t="n">
         <v>57727</v>
@@ -7086,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602896</v>
+        <v>602703</v>
       </c>
       <c r="R65" t="n">
-        <v>6979327</v>
+        <v>6979746</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7126,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7255,7 +7247,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129627767</v>
+        <v>129627675</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7290,10 +7282,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602703</v>
+        <v>602835</v>
       </c>
       <c r="R67" t="n">
-        <v>6979746</v>
+        <v>6979550</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7330,7 +7322,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7459,7 +7451,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627675</v>
+        <v>129627682</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -7494,10 +7486,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602835</v>
+        <v>602720</v>
       </c>
       <c r="R69" t="n">
-        <v>6979550</v>
+        <v>6979665</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7561,10 +7553,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627682</v>
+        <v>129627770</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7572,21 +7564,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7596,10 +7588,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602720</v>
+        <v>602876</v>
       </c>
       <c r="R70" t="n">
-        <v>6979665</v>
+        <v>6979597</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7636,7 +7628,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 ex, övriga/lockläten läten.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7663,10 +7655,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129627770</v>
+        <v>129627676</v>
       </c>
       <c r="B71" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7674,21 +7666,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7698,10 +7690,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602876</v>
+        <v>602825</v>
       </c>
       <c r="R71" t="n">
-        <v>6979597</v>
+        <v>6979660</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7738,7 +7730,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>2 ex, övriga/lockläten läten.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7765,7 +7757,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129627769</v>
+        <v>129627679</v>
       </c>
       <c r="B72" t="n">
         <v>57727</v>
@@ -7800,10 +7792,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602761</v>
+        <v>602740</v>
       </c>
       <c r="R72" t="n">
-        <v>6979565</v>
+        <v>6979774</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7840,7 +7832,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7867,7 +7859,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129627679</v>
+        <v>129627769</v>
       </c>
       <c r="B73" t="n">
         <v>57727</v>
@@ -7902,10 +7894,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602740</v>
+        <v>602761</v>
       </c>
       <c r="R73" t="n">
-        <v>6979774</v>
+        <v>6979565</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7942,7 +7934,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7969,7 +7961,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129627676</v>
+        <v>129627669</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7998,16 +7990,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>602825</v>
+        <v>602791</v>
       </c>
       <c r="R74" t="n">
-        <v>6979660</v>
+        <v>6979625</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Sannolikt ett påbörjat bohål av vad som kan vara tretåig hackspett. Sitter 2 meter ovan mark i en asp. Bohålet är inte klart, men öppningen mättes till omkring 4 centimeter.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3956,10 +3956,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627774</v>
+        <v>129627685</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,21 +3967,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602748</v>
+        <v>602797</v>
       </c>
       <c r="R34" t="n">
-        <v>6979628</v>
+        <v>6979575</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,6 +4027,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4053,10 +4058,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627685</v>
+        <v>129627774</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4064,21 +4069,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4088,10 +4093,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602797</v>
+        <v>602748</v>
       </c>
       <c r="R35" t="n">
-        <v>6979575</v>
+        <v>6979628</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,11 +4129,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4252,7 +4252,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627687</v>
+        <v>129627762</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602794</v>
+        <v>602818</v>
       </c>
       <c r="R37" t="n">
-        <v>6979575</v>
+        <v>6979362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,7 +4354,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627762</v>
+        <v>129627684</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602818</v>
+        <v>602714</v>
       </c>
       <c r="R38" t="n">
-        <v>6979362</v>
+        <v>6979668</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,7 +4456,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627684</v>
+        <v>129627687</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602714</v>
+        <v>602794</v>
       </c>
       <c r="R39" t="n">
-        <v>6979668</v>
+        <v>6979575</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627779</v>
+        <v>129627667</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602869</v>
+        <v>602690</v>
       </c>
       <c r="R42" t="n">
-        <v>6979601</v>
+        <v>6979583</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R43" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5844,10 +5844,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129627775</v>
+        <v>129627694</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>91567</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602854</v>
+        <v>602905</v>
       </c>
       <c r="R53" t="n">
-        <v>6979675</v>
+        <v>6979425</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129627694</v>
+        <v>129627775</v>
       </c>
       <c r="B54" t="n">
-        <v>91567</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5952,21 +5952,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>602905</v>
+        <v>602854</v>
       </c>
       <c r="R54" t="n">
-        <v>6979425</v>
+        <v>6979675</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7043,32 +7043,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627767</v>
+        <v>129627777</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602703</v>
+        <v>602720</v>
       </c>
       <c r="R65" t="n">
-        <v>6979746</v>
+        <v>6979669</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>150 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,32 +7145,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627777</v>
+        <v>129627767</v>
       </c>
       <c r="B66" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602720</v>
+        <v>602703</v>
       </c>
       <c r="R66" t="n">
-        <v>6979669</v>
+        <v>6979746</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>150 stycken ca</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>129627765</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>129627689</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>129627764</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129627686</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>129627771</v>
       </c>
       <c r="B33" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627685</v>
+        <v>129627774</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,21 +3967,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602797</v>
+        <v>602748</v>
       </c>
       <c r="R34" t="n">
-        <v>6979575</v>
+        <v>6979628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,11 +4027,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4058,32 +4053,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627774</v>
+        <v>129627690</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>97627</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4093,10 +4088,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602748</v>
+        <v>602770</v>
       </c>
       <c r="R35" t="n">
-        <v>6979628</v>
+        <v>6979694</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,32 +4150,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627690</v>
+        <v>129627685</v>
       </c>
       <c r="B36" t="n">
-        <v>97598</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4190,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602770</v>
+        <v>602797</v>
       </c>
       <c r="R36" t="n">
-        <v>6979694</v>
+        <v>6979575</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4226,6 +4221,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4255,7 +4255,7 @@
         <v>129627762</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>129627684</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>129627687</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>129627780</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>129627691</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>129627667</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627779</v>
+        <v>129627692</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4860,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602869</v>
+        <v>602707</v>
       </c>
       <c r="R43" t="n">
-        <v>6979601</v>
+        <v>6979618</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4946,10 +4946,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627692</v>
+        <v>129627779</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4957,21 +4957,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602707</v>
+        <v>602869</v>
       </c>
       <c r="R44" t="n">
-        <v>6979618</v>
+        <v>6979601</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,7 +5046,7 @@
         <v>129627671</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>129627674</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>129627695</v>
       </c>
       <c r="B47" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129627778</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129627688</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>129627768</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5645,32 +5645,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627666</v>
+        <v>129627677</v>
       </c>
       <c r="B51" t="n">
-        <v>91517</v>
+        <v>57730</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>602670</v>
+        <v>602776</v>
       </c>
       <c r="R51" t="n">
-        <v>6979481</v>
+        <v>6979680</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5716,6 +5716,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5742,32 +5747,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129627677</v>
+        <v>129627666</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5777,10 +5782,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>602776</v>
+        <v>602670</v>
       </c>
       <c r="R52" t="n">
-        <v>6979680</v>
+        <v>6979481</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5813,11 +5818,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5847,7 +5847,7 @@
         <v>129627694</v>
       </c>
       <c r="B53" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>129627775</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>129627693</v>
       </c>
       <c r="B55" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>129627772</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>129627773</v>
       </c>
       <c r="B57" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>129627672</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>129627766</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>129627678</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129627673</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>129627681</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>129627763</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>129627670</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7043,32 +7043,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627777</v>
+        <v>129627767</v>
       </c>
       <c r="B65" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602720</v>
+        <v>602703</v>
       </c>
       <c r="R65" t="n">
-        <v>6979669</v>
+        <v>6979746</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>150 stycken ca</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,32 +7145,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627767</v>
+        <v>129627777</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602703</v>
+        <v>602720</v>
       </c>
       <c r="R66" t="n">
-        <v>6979746</v>
+        <v>6979669</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>150 stycken ca</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7250,7 +7250,7 @@
         <v>129627675</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>129627680</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>129627682</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>129627770</v>
       </c>
       <c r="B70" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>129627676</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>129627679</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>129627769</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>129627669</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -5645,32 +5645,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627677</v>
+        <v>129627666</v>
       </c>
       <c r="B51" t="n">
-        <v>57730</v>
+        <v>91545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>602776</v>
+        <v>602670</v>
       </c>
       <c r="R51" t="n">
-        <v>6979680</v>
+        <v>6979481</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5716,11 +5716,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5747,32 +5742,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129627666</v>
+        <v>129627677</v>
       </c>
       <c r="B52" t="n">
-        <v>91545</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>602670</v>
+        <v>602776</v>
       </c>
       <c r="R52" t="n">
-        <v>6979481</v>
+        <v>6979680</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5818,6 +5813,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7043,32 +7043,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627767</v>
+        <v>129627777</v>
       </c>
       <c r="B65" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602703</v>
+        <v>602720</v>
       </c>
       <c r="R65" t="n">
-        <v>6979746</v>
+        <v>6979669</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>150 stycken ca</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,32 +7145,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627777</v>
+        <v>129627767</v>
       </c>
       <c r="B66" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602720</v>
+        <v>602703</v>
       </c>
       <c r="R66" t="n">
-        <v>6979669</v>
+        <v>6979746</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>150 stycken ca</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3454,7 +3454,7 @@
         <v>129627765</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>129627689</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627764</v>
+        <v>129627686</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602916</v>
+        <v>602797</v>
       </c>
       <c r="R31" t="n">
-        <v>6979371</v>
+        <v>6979572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627686</v>
+        <v>129627764</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602797</v>
+        <v>602916</v>
       </c>
       <c r="R32" t="n">
-        <v>6979572</v>
+        <v>6979371</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3862,7 +3862,7 @@
         <v>129627771</v>
       </c>
       <c r="B33" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3956,32 +3956,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627774</v>
+        <v>129627690</v>
       </c>
       <c r="B34" t="n">
-        <v>80175</v>
+        <v>97639</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602748</v>
+        <v>602770</v>
       </c>
       <c r="R34" t="n">
-        <v>6979628</v>
+        <v>6979694</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,32 +4053,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627690</v>
+        <v>129627774</v>
       </c>
       <c r="B35" t="n">
-        <v>97627</v>
+        <v>80180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602770</v>
+        <v>602748</v>
       </c>
       <c r="R35" t="n">
-        <v>6979694</v>
+        <v>6979628</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,7 +4153,7 @@
         <v>129627685</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>129627762</v>
       </c>
       <c r="B37" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4354,10 +4354,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627684</v>
+        <v>129627687</v>
       </c>
       <c r="B38" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602714</v>
+        <v>602794</v>
       </c>
       <c r="R38" t="n">
-        <v>6979668</v>
+        <v>6979575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627687</v>
+        <v>129627684</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602794</v>
+        <v>602714</v>
       </c>
       <c r="R39" t="n">
-        <v>6979575</v>
+        <v>6979668</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4558,10 +4558,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627780</v>
+        <v>129627691</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>602750</v>
+        <v>602779</v>
       </c>
       <c r="R40" t="n">
-        <v>6979588</v>
+        <v>6979669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627691</v>
+        <v>129627780</v>
       </c>
       <c r="B41" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4666,21 +4666,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602779</v>
+        <v>602750</v>
       </c>
       <c r="R41" t="n">
-        <v>6979669</v>
+        <v>6979588</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627667</v>
+        <v>129627671</v>
       </c>
       <c r="B42" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602690</v>
+        <v>602903</v>
       </c>
       <c r="R42" t="n">
-        <v>6979583</v>
+        <v>6979431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4823,6 +4823,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4849,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627692</v>
+        <v>129627667</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,21 +4865,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4884,10 +4889,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602707</v>
+        <v>602690</v>
       </c>
       <c r="R43" t="n">
-        <v>6979618</v>
+        <v>6979583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4946,10 +4951,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627779</v>
+        <v>129627692</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4957,21 +4962,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602869</v>
+        <v>602707</v>
       </c>
       <c r="R44" t="n">
-        <v>6979601</v>
+        <v>6979618</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5043,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129627671</v>
+        <v>129627779</v>
       </c>
       <c r="B45" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5054,21 +5059,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5078,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>602903</v>
+        <v>602869</v>
       </c>
       <c r="R45" t="n">
-        <v>6979431</v>
+        <v>6979601</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5114,11 +5119,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5148,7 +5148,7 @@
         <v>129627674</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>129627695</v>
       </c>
       <c r="B47" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>129627778</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>129627688</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>129627768</v>
       </c>
       <c r="B50" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>129627666</v>
       </c>
       <c r="B51" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>129627677</v>
       </c>
       <c r="B52" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>129627694</v>
       </c>
       <c r="B53" t="n">
-        <v>91595</v>
+        <v>91601</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>129627775</v>
       </c>
       <c r="B54" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129627693</v>
+        <v>129627772</v>
       </c>
       <c r="B55" t="n">
-        <v>78827</v>
+        <v>80180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6049,21 +6049,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>602722</v>
+        <v>602908</v>
       </c>
       <c r="R55" t="n">
-        <v>6979623</v>
+        <v>6979328</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6135,10 +6135,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129627772</v>
+        <v>129627693</v>
       </c>
       <c r="B56" t="n">
-        <v>80175</v>
+        <v>78832</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6146,21 +6146,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6170,10 +6170,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>602908</v>
+        <v>602722</v>
       </c>
       <c r="R56" t="n">
-        <v>6979328</v>
+        <v>6979623</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6235,7 +6235,7 @@
         <v>129627773</v>
       </c>
       <c r="B57" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129627672</v>
+        <v>129627766</v>
       </c>
       <c r="B58" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,10 +6364,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602872</v>
+        <v>602935</v>
       </c>
       <c r="R58" t="n">
-        <v>6979492</v>
+        <v>6979466</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6431,10 +6431,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129627766</v>
+        <v>129627673</v>
       </c>
       <c r="B59" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602935</v>
+        <v>602857</v>
       </c>
       <c r="R59" t="n">
-        <v>6979466</v>
+        <v>6979536</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6536,7 +6536,7 @@
         <v>129627678</v>
       </c>
       <c r="B60" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129627673</v>
+        <v>129627672</v>
       </c>
       <c r="B61" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602857</v>
+        <v>602872</v>
       </c>
       <c r="R61" t="n">
-        <v>6979536</v>
+        <v>6979492</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129627681</v>
+        <v>129627670</v>
       </c>
       <c r="B62" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602787</v>
+        <v>602850</v>
       </c>
       <c r="R62" t="n">
-        <v>6979696</v>
+        <v>6979445</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129627763</v>
+        <v>129627681</v>
       </c>
       <c r="B63" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602896</v>
+        <v>602787</v>
       </c>
       <c r="R63" t="n">
-        <v>6979327</v>
+        <v>6979696</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129627670</v>
+        <v>129627763</v>
       </c>
       <c r="B64" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602850</v>
+        <v>602896</v>
       </c>
       <c r="R64" t="n">
-        <v>6979445</v>
+        <v>6979327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7043,32 +7043,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627777</v>
+        <v>129627767</v>
       </c>
       <c r="B65" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602720</v>
+        <v>602703</v>
       </c>
       <c r="R65" t="n">
-        <v>6979669</v>
+        <v>6979746</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>150 stycken ca</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,32 +7145,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627767</v>
+        <v>129627777</v>
       </c>
       <c r="B66" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602703</v>
+        <v>602720</v>
       </c>
       <c r="R66" t="n">
-        <v>6979746</v>
+        <v>6979669</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>150 stycken ca</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7247,10 +7247,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129627675</v>
+        <v>129627680</v>
       </c>
       <c r="B67" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602835</v>
+        <v>602732</v>
       </c>
       <c r="R67" t="n">
-        <v>6979550</v>
+        <v>6979746</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627680</v>
+        <v>129627675</v>
       </c>
       <c r="B68" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602732</v>
+        <v>602835</v>
       </c>
       <c r="R68" t="n">
-        <v>6979746</v>
+        <v>6979550</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
         <v>129627682</v>
       </c>
       <c r="B69" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>129627770</v>
       </c>
       <c r="B70" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129627676</v>
+        <v>129627769</v>
       </c>
       <c r="B71" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602825</v>
+        <v>602761</v>
       </c>
       <c r="R71" t="n">
-        <v>6979660</v>
+        <v>6979565</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7760,7 +7760,7 @@
         <v>129627679</v>
       </c>
       <c r="B72" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7859,10 +7859,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129627769</v>
+        <v>129627676</v>
       </c>
       <c r="B73" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602761</v>
+        <v>602825</v>
       </c>
       <c r="R73" t="n">
-        <v>6979565</v>
+        <v>6979660</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7958,116 +7958,6 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>129627669</v>
-      </c>
-      <c r="B74" t="n">
-        <v>57730</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Kroktjärnsberget, Mpd</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>602791</v>
-      </c>
-      <c r="R74" t="n">
-        <v>6979625</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Liden</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Sannolikt ett påbörjat bohål av vad som kan vara tretåig hackspett. Sitter 2 meter ovan mark i en asp. Bohålet är inte klart, men öppningen mättes till omkring 4 centimeter.</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3451,10 +3451,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627765</v>
+        <v>129627689</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3462,16 +3462,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602904</v>
+        <v>602773</v>
       </c>
       <c r="R29" t="n">
-        <v>6979415</v>
+        <v>6979714</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall färska spår.</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3553,32 +3553,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627689</v>
+        <v>129627771</v>
       </c>
       <c r="B30" t="n">
-        <v>57732</v>
+        <v>97640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602773</v>
+        <v>602782</v>
       </c>
       <c r="R30" t="n">
-        <v>6979714</v>
+        <v>6979624</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3624,11 +3624,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3655,10 +3650,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627686</v>
+        <v>129627774</v>
       </c>
       <c r="B31" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,21 +3661,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3690,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602797</v>
+        <v>602748</v>
       </c>
       <c r="R31" t="n">
-        <v>6979572</v>
+        <v>6979628</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3726,11 +3721,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3757,32 +3747,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627764</v>
+        <v>129627690</v>
       </c>
       <c r="B32" t="n">
-        <v>57735</v>
+        <v>97640</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3792,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602916</v>
+        <v>602770</v>
       </c>
       <c r="R32" t="n">
-        <v>6979371</v>
+        <v>6979694</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3828,11 +3818,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3859,32 +3844,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627771</v>
+        <v>129627780</v>
       </c>
       <c r="B33" t="n">
-        <v>97639</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3894,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602782</v>
+        <v>602750</v>
       </c>
       <c r="R33" t="n">
-        <v>6979624</v>
+        <v>6979588</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,32 +3941,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627690</v>
+        <v>129627691</v>
       </c>
       <c r="B34" t="n">
-        <v>97639</v>
+        <v>80181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3976,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602770</v>
+        <v>602779</v>
       </c>
       <c r="R34" t="n">
-        <v>6979694</v>
+        <v>6979669</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627774</v>
+        <v>129627667</v>
       </c>
       <c r="B35" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4064,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4088,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602748</v>
+        <v>602690</v>
       </c>
       <c r="R35" t="n">
-        <v>6979628</v>
+        <v>6979583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4150,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627685</v>
+        <v>129627779</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4161,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602797</v>
+        <v>602869</v>
       </c>
       <c r="R36" t="n">
-        <v>6979575</v>
+        <v>6979601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4221,11 +4206,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4252,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627762</v>
+        <v>129627692</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4263,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602818</v>
+        <v>602707</v>
       </c>
       <c r="R37" t="n">
-        <v>6979362</v>
+        <v>6979618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4323,11 +4303,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627687</v>
+        <v>129627778</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4365,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602794</v>
+        <v>602935</v>
       </c>
       <c r="R38" t="n">
-        <v>6979575</v>
+        <v>6979389</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4425,11 +4400,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627684</v>
+        <v>129627695</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>88987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4467,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602714</v>
+        <v>602860</v>
       </c>
       <c r="R39" t="n">
-        <v>6979668</v>
+        <v>6979447</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4527,11 +4497,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,32 +4523,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627691</v>
+        <v>129627666</v>
       </c>
       <c r="B40" t="n">
-        <v>80180</v>
+        <v>91552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4558,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>602779</v>
+        <v>602670</v>
       </c>
       <c r="R40" t="n">
-        <v>6979669</v>
+        <v>6979481</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4655,10 +4620,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627780</v>
+        <v>129627694</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>91602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4666,21 +4631,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4690,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602750</v>
+        <v>602905</v>
       </c>
       <c r="R41" t="n">
-        <v>6979588</v>
+        <v>6979425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4752,10 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627671</v>
+        <v>129627775</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4728,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4787,10 +4752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602903</v>
+        <v>602854</v>
       </c>
       <c r="R42" t="n">
-        <v>6979431</v>
+        <v>6979675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4823,11 +4788,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4854,10 +4814,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627667</v>
+        <v>129627693</v>
       </c>
       <c r="B43" t="n">
-        <v>91587</v>
+        <v>78833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,21 +4825,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4889,10 +4849,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602690</v>
+        <v>602722</v>
       </c>
       <c r="R43" t="n">
-        <v>6979583</v>
+        <v>6979623</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,10 +4911,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627692</v>
+        <v>129627772</v>
       </c>
       <c r="B44" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4986,10 +4946,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602707</v>
+        <v>602908</v>
       </c>
       <c r="R44" t="n">
-        <v>6979618</v>
+        <v>6979328</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,10 +5008,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129627779</v>
+        <v>129627773</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,21 +5019,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5043,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>602869</v>
+        <v>602909</v>
       </c>
       <c r="R45" t="n">
-        <v>6979601</v>
+        <v>6979335</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5145,32 +5105,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129627674</v>
+        <v>129627777</v>
       </c>
       <c r="B46" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5180,10 +5140,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>602809</v>
+        <v>602720</v>
       </c>
       <c r="R46" t="n">
-        <v>6979547</v>
+        <v>6979669</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5220,7 +5180,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 ex födosökande</t>
+          <t>150 stycken ca</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5247,10 +5207,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129627695</v>
+        <v>129627770</v>
       </c>
       <c r="B47" t="n">
-        <v>88986</v>
+        <v>57896</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5258,21 +5218,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5282,10 +5242,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>602860</v>
+        <v>602876</v>
       </c>
       <c r="R47" t="n">
-        <v>6979447</v>
+        <v>6979597</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5318,6 +5278,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2 ex, övriga/lockläten läten.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5344,10 +5309,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129627778</v>
+        <v>129627765</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5355,21 +5320,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5379,10 +5344,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>602935</v>
+        <v>602904</v>
       </c>
       <c r="R48" t="n">
-        <v>6979389</v>
+        <v>6979415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5415,6 +5380,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på tall färska spår.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5441,10 +5411,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129627688</v>
+        <v>129627686</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5476,10 +5446,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>602759</v>
+        <v>602797</v>
       </c>
       <c r="R49" t="n">
-        <v>6979557</v>
+        <v>6979572</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,10 +5513,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627768</v>
+        <v>129627764</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5578,10 +5548,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602780</v>
+        <v>602916</v>
       </c>
       <c r="R50" t="n">
-        <v>6979618</v>
+        <v>6979371</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5618,7 +5588,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett, färska spår på tall.</t>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5645,32 +5615,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627666</v>
+        <v>129627685</v>
       </c>
       <c r="B51" t="n">
-        <v>91551</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5680,10 +5650,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>602670</v>
+        <v>602797</v>
       </c>
       <c r="R51" t="n">
-        <v>6979481</v>
+        <v>6979575</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5716,6 +5686,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5742,10 +5717,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129627677</v>
+        <v>129627762</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5777,10 +5752,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>602776</v>
+        <v>602818</v>
       </c>
       <c r="R52" t="n">
-        <v>6979680</v>
+        <v>6979362</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5817,7 +5792,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5844,10 +5819,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129627694</v>
+        <v>129627687</v>
       </c>
       <c r="B53" t="n">
-        <v>91601</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5855,21 +5830,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5879,10 +5854,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602905</v>
+        <v>602794</v>
       </c>
       <c r="R53" t="n">
-        <v>6979425</v>
+        <v>6979575</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5915,6 +5890,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5941,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129627775</v>
+        <v>129627684</v>
       </c>
       <c r="B54" t="n">
-        <v>80180</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5952,21 +5932,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5976,10 +5956,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>602854</v>
+        <v>602714</v>
       </c>
       <c r="R54" t="n">
-        <v>6979675</v>
+        <v>6979668</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6012,6 +5992,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6038,10 +6023,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129627772</v>
+        <v>129627671</v>
       </c>
       <c r="B55" t="n">
-        <v>80180</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6049,21 +6034,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6073,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>602908</v>
+        <v>602903</v>
       </c>
       <c r="R55" t="n">
-        <v>6979328</v>
+        <v>6979431</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6109,6 +6094,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6135,10 +6125,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129627693</v>
+        <v>129627674</v>
       </c>
       <c r="B56" t="n">
-        <v>78832</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6146,21 +6136,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6170,10 +6160,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>602722</v>
+        <v>602809</v>
       </c>
       <c r="R56" t="n">
-        <v>6979623</v>
+        <v>6979547</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6206,6 +6196,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6232,10 +6227,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129627773</v>
+        <v>129627688</v>
       </c>
       <c r="B57" t="n">
-        <v>80180</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6243,21 +6238,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6267,10 +6262,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>602909</v>
+        <v>602759</v>
       </c>
       <c r="R57" t="n">
-        <v>6979335</v>
+        <v>6979557</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6303,6 +6298,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6329,10 +6329,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129627766</v>
+        <v>129627768</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,10 +6364,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602935</v>
+        <v>602780</v>
       </c>
       <c r="R58" t="n">
-        <v>6979466</v>
+        <v>6979618</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>Ringhack av tretåig hackspett, färska spår på tall.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6431,10 +6431,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129627673</v>
+        <v>129627677</v>
       </c>
       <c r="B59" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602857</v>
+        <v>602776</v>
       </c>
       <c r="R59" t="n">
-        <v>6979536</v>
+        <v>6979680</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6533,10 +6533,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129627678</v>
+        <v>129627766</v>
       </c>
       <c r="B60" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602750</v>
+        <v>602935</v>
       </c>
       <c r="R60" t="n">
-        <v>6979758</v>
+        <v>6979466</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6635,10 +6635,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129627672</v>
+        <v>129627673</v>
       </c>
       <c r="B61" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602872</v>
+        <v>602857</v>
       </c>
       <c r="R61" t="n">
-        <v>6979492</v>
+        <v>6979536</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129627670</v>
+        <v>129627678</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602850</v>
+        <v>602750</v>
       </c>
       <c r="R62" t="n">
-        <v>6979445</v>
+        <v>6979758</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129627681</v>
+        <v>129627672</v>
       </c>
       <c r="B63" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602787</v>
+        <v>602872</v>
       </c>
       <c r="R63" t="n">
-        <v>6979696</v>
+        <v>6979492</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129627763</v>
+        <v>129627670</v>
       </c>
       <c r="B64" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602896</v>
+        <v>602850</v>
       </c>
       <c r="R64" t="n">
-        <v>6979327</v>
+        <v>6979445</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7043,10 +7043,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627767</v>
+        <v>129627681</v>
       </c>
       <c r="B65" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602703</v>
+        <v>602787</v>
       </c>
       <c r="R65" t="n">
-        <v>6979746</v>
+        <v>6979696</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,32 +7145,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627777</v>
+        <v>129627763</v>
       </c>
       <c r="B66" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602720</v>
+        <v>602896</v>
       </c>
       <c r="R66" t="n">
-        <v>6979669</v>
+        <v>6979327</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>150 stycken ca</t>
+          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7247,10 +7247,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129627680</v>
+        <v>129627767</v>
       </c>
       <c r="B67" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602732</v>
+        <v>602703</v>
       </c>
       <c r="R67" t="n">
         <v>6979746</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7349,10 +7349,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627675</v>
+        <v>129627680</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602835</v>
+        <v>602732</v>
       </c>
       <c r="R68" t="n">
-        <v>6979550</v>
+        <v>6979746</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7451,10 +7451,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627682</v>
+        <v>129627675</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602720</v>
+        <v>602835</v>
       </c>
       <c r="R69" t="n">
-        <v>6979665</v>
+        <v>6979550</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7553,10 +7553,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627770</v>
+        <v>129627682</v>
       </c>
       <c r="B70" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7564,21 +7564,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602876</v>
+        <v>602720</v>
       </c>
       <c r="R70" t="n">
-        <v>6979597</v>
+        <v>6979665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>2 ex, övriga/lockläten läten.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7658,7 +7658,7 @@
         <v>129627769</v>
       </c>
       <c r="B71" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>129627679</v>
       </c>
       <c r="B72" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>129627676</v>
       </c>
       <c r="B73" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B35" t="n">
-        <v>91588</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R35" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627779</v>
+        <v>129627692</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602869</v>
+        <v>602707</v>
       </c>
       <c r="R36" t="n">
-        <v>6979601</v>
+        <v>6979618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627692</v>
+        <v>129627667</v>
       </c>
       <c r="B37" t="n">
-        <v>80181</v>
+        <v>91588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602707</v>
+        <v>602690</v>
       </c>
       <c r="R37" t="n">
-        <v>6979618</v>
+        <v>6979583</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627694</v>
+        <v>129627775</v>
       </c>
       <c r="B41" t="n">
-        <v>91602</v>
+        <v>80181</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4631,21 +4631,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602905</v>
+        <v>602854</v>
       </c>
       <c r="R41" t="n">
-        <v>6979425</v>
+        <v>6979675</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627775</v>
+        <v>129627694</v>
       </c>
       <c r="B42" t="n">
-        <v>80181</v>
+        <v>91602</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602854</v>
+        <v>602905</v>
       </c>
       <c r="R42" t="n">
-        <v>6979675</v>
+        <v>6979425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129627771</v>
       </c>
       <c r="B30" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>129627774</v>
       </c>
       <c r="B31" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129627690</v>
       </c>
       <c r="B32" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>129627780</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>129627691</v>
       </c>
       <c r="B34" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>129627779</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>129627692</v>
       </c>
       <c r="B36" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>129627667</v>
       </c>
       <c r="B37" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627778</v>
+        <v>129627695</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>88992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602935</v>
+        <v>602860</v>
       </c>
       <c r="R38" t="n">
-        <v>6979389</v>
+        <v>6979447</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627695</v>
+        <v>129627778</v>
       </c>
       <c r="B39" t="n">
-        <v>88987</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4437,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602860</v>
+        <v>602935</v>
       </c>
       <c r="R39" t="n">
-        <v>6979447</v>
+        <v>6979389</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,7 +4526,7 @@
         <v>129627666</v>
       </c>
       <c r="B40" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>129627775</v>
       </c>
       <c r="B41" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>129627694</v>
       </c>
       <c r="B42" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627693</v>
+        <v>129627772</v>
       </c>
       <c r="B43" t="n">
-        <v>78833</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,21 +4825,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602722</v>
+        <v>602908</v>
       </c>
       <c r="R43" t="n">
-        <v>6979623</v>
+        <v>6979328</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627772</v>
+        <v>129627693</v>
       </c>
       <c r="B44" t="n">
-        <v>80181</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4922,21 +4922,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602908</v>
+        <v>602722</v>
       </c>
       <c r="R44" t="n">
-        <v>6979328</v>
+        <v>6979623</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5011,7 +5011,7 @@
         <v>129627773</v>
       </c>
       <c r="B45" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>129627777</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627779</v>
+        <v>129627667</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602869</v>
+        <v>602690</v>
       </c>
       <c r="R35" t="n">
-        <v>6979601</v>
+        <v>6979583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627692</v>
+        <v>129627779</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602707</v>
+        <v>602869</v>
       </c>
       <c r="R36" t="n">
-        <v>6979618</v>
+        <v>6979601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627667</v>
+        <v>129627692</v>
       </c>
       <c r="B37" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602690</v>
+        <v>602707</v>
       </c>
       <c r="R37" t="n">
-        <v>6979583</v>
+        <v>6979618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627775</v>
+        <v>129627694</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>91607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4631,21 +4631,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602854</v>
+        <v>602905</v>
       </c>
       <c r="R41" t="n">
-        <v>6979675</v>
+        <v>6979425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627694</v>
+        <v>129627775</v>
       </c>
       <c r="B42" t="n">
-        <v>91607</v>
+        <v>80186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602905</v>
+        <v>602854</v>
       </c>
       <c r="R42" t="n">
-        <v>6979425</v>
+        <v>6979675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627772</v>
+        <v>129627693</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>78838</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,21 +4825,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602908</v>
+        <v>602722</v>
       </c>
       <c r="R43" t="n">
-        <v>6979328</v>
+        <v>6979623</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627693</v>
+        <v>129627772</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4922,21 +4922,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602722</v>
+        <v>602908</v>
       </c>
       <c r="R44" t="n">
-        <v>6979623</v>
+        <v>6979328</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627780</v>
+        <v>129627691</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602750</v>
+        <v>602779</v>
       </c>
       <c r="R33" t="n">
-        <v>6979588</v>
+        <v>6979669</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627691</v>
+        <v>129627780</v>
       </c>
       <c r="B34" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602779</v>
+        <v>602750</v>
       </c>
       <c r="R34" t="n">
-        <v>6979669</v>
+        <v>6979588</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R35" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627779</v>
+        <v>129627667</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602869</v>
+        <v>602690</v>
       </c>
       <c r="R36" t="n">
-        <v>6979601</v>
+        <v>6979583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627694</v>
+        <v>129627775</v>
       </c>
       <c r="B41" t="n">
-        <v>91607</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4631,21 +4631,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602905</v>
+        <v>602854</v>
       </c>
       <c r="R41" t="n">
-        <v>6979425</v>
+        <v>6979675</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627775</v>
+        <v>129627694</v>
       </c>
       <c r="B42" t="n">
-        <v>80186</v>
+        <v>91607</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602854</v>
+        <v>602905</v>
       </c>
       <c r="R42" t="n">
-        <v>6979675</v>
+        <v>6979425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627667</v>
+        <v>129627692</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602690</v>
+        <v>602707</v>
       </c>
       <c r="R36" t="n">
-        <v>6979583</v>
+        <v>6979618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627692</v>
+        <v>129627667</v>
       </c>
       <c r="B37" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602707</v>
+        <v>602690</v>
       </c>
       <c r="R37" t="n">
-        <v>6979618</v>
+        <v>6979583</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627775</v>
+        <v>129627694</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>91607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4631,21 +4631,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602854</v>
+        <v>602905</v>
       </c>
       <c r="R41" t="n">
-        <v>6979675</v>
+        <v>6979425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627694</v>
+        <v>129627775</v>
       </c>
       <c r="B42" t="n">
-        <v>91607</v>
+        <v>80186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602905</v>
+        <v>602854</v>
       </c>
       <c r="R42" t="n">
-        <v>6979425</v>
+        <v>6979675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -7451,7 +7451,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627675</v>
+        <v>129627682</v>
       </c>
       <c r="B69" t="n">
         <v>57736</v>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602835</v>
+        <v>602720</v>
       </c>
       <c r="R69" t="n">
-        <v>6979550</v>
+        <v>6979665</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627682</v>
+        <v>129627675</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602720</v>
+        <v>602835</v>
       </c>
       <c r="R70" t="n">
-        <v>6979665</v>
+        <v>6979550</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129627771</v>
       </c>
       <c r="B30" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129627690</v>
       </c>
       <c r="B32" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627779</v>
+        <v>129627667</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602869</v>
+        <v>602690</v>
       </c>
       <c r="R35" t="n">
-        <v>6979601</v>
+        <v>6979583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B37" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R37" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4332,7 +4332,7 @@
         <v>129627695</v>
       </c>
       <c r="B38" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>129627666</v>
       </c>
       <c r="B40" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>129627694</v>
       </c>
       <c r="B41" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>129627777</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627682</v>
+        <v>129627675</v>
       </c>
       <c r="B69" t="n">
         <v>57736</v>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602720</v>
+        <v>602835</v>
       </c>
       <c r="R69" t="n">
-        <v>6979665</v>
+        <v>6979550</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627675</v>
+        <v>129627682</v>
       </c>
       <c r="B70" t="n">
         <v>57736</v>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602835</v>
+        <v>602720</v>
       </c>
       <c r="R70" t="n">
-        <v>6979550</v>
+        <v>6979665</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129627771</v>
       </c>
       <c r="B30" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129627690</v>
       </c>
       <c r="B32" t="n">
-        <v>97649</v>
+        <v>97651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B35" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R35" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627692</v>
+        <v>129627667</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602707</v>
+        <v>602690</v>
       </c>
       <c r="R36" t="n">
-        <v>6979618</v>
+        <v>6979583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627779</v>
+        <v>129627692</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602869</v>
+        <v>602707</v>
       </c>
       <c r="R37" t="n">
-        <v>6979601</v>
+        <v>6979618</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627695</v>
+        <v>129627778</v>
       </c>
       <c r="B38" t="n">
-        <v>88996</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602860</v>
+        <v>602935</v>
       </c>
       <c r="R38" t="n">
-        <v>6979447</v>
+        <v>6979389</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627778</v>
+        <v>129627695</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4437,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602935</v>
+        <v>602860</v>
       </c>
       <c r="R39" t="n">
-        <v>6979389</v>
+        <v>6979447</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,7 +4526,7 @@
         <v>129627666</v>
       </c>
       <c r="B40" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>129627694</v>
       </c>
       <c r="B41" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>129627777</v>
       </c>
       <c r="B46" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627779</v>
+        <v>129627667</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602869</v>
+        <v>602690</v>
       </c>
       <c r="R35" t="n">
-        <v>6979601</v>
+        <v>6979583</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R36" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4038,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627667</v>
+        <v>129627779</v>
       </c>
       <c r="B35" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602690</v>
+        <v>602869</v>
       </c>
       <c r="R35" t="n">
-        <v>6979583</v>
+        <v>6979601</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627779</v>
+        <v>129627667</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602869</v>
+        <v>602690</v>
       </c>
       <c r="R36" t="n">
-        <v>6979601</v>
+        <v>6979583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3556,7 +3556,7 @@
         <v>129627771</v>
       </c>
       <c r="B30" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,32 +3650,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627774</v>
+        <v>129627690</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>97661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602748</v>
+        <v>602770</v>
       </c>
       <c r="R31" t="n">
-        <v>6979628</v>
+        <v>6979694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627690</v>
+        <v>129627774</v>
       </c>
       <c r="B32" t="n">
-        <v>97651</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602770</v>
+        <v>602748</v>
       </c>
       <c r="R32" t="n">
-        <v>6979694</v>
+        <v>6979628</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627667</v>
+        <v>129627692</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4146,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602690</v>
+        <v>602707</v>
       </c>
       <c r="R36" t="n">
-        <v>6979583</v>
+        <v>6979618</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627692</v>
+        <v>129627667</v>
       </c>
       <c r="B37" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602707</v>
+        <v>602690</v>
       </c>
       <c r="R37" t="n">
-        <v>6979618</v>
+        <v>6979583</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627778</v>
+        <v>129627695</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602935</v>
+        <v>602860</v>
       </c>
       <c r="R38" t="n">
-        <v>6979389</v>
+        <v>6979447</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627695</v>
+        <v>129627778</v>
       </c>
       <c r="B39" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4437,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602860</v>
+        <v>602935</v>
       </c>
       <c r="R39" t="n">
-        <v>6979447</v>
+        <v>6979389</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627694</v>
+        <v>129627775</v>
       </c>
       <c r="B41" t="n">
-        <v>91613</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4631,21 +4631,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602905</v>
+        <v>602854</v>
       </c>
       <c r="R41" t="n">
-        <v>6979425</v>
+        <v>6979675</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627775</v>
+        <v>129627694</v>
       </c>
       <c r="B42" t="n">
-        <v>80186</v>
+        <v>91613</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602854</v>
+        <v>602905</v>
       </c>
       <c r="R42" t="n">
-        <v>6979675</v>
+        <v>6979425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5108,7 +5108,7 @@
         <v>129627777</v>
       </c>
       <c r="B46" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4814,10 +4814,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627693</v>
+        <v>129627772</v>
       </c>
       <c r="B43" t="n">
-        <v>78838</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,21 +4825,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602722</v>
+        <v>602908</v>
       </c>
       <c r="R43" t="n">
-        <v>6979623</v>
+        <v>6979328</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627772</v>
+        <v>129627693</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4922,21 +4922,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602908</v>
+        <v>602722</v>
       </c>
       <c r="R44" t="n">
-        <v>6979328</v>
+        <v>6979623</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -7655,7 +7655,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129627769</v>
+        <v>129627676</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602761</v>
+        <v>602825</v>
       </c>
       <c r="R71" t="n">
-        <v>6979565</v>
+        <v>6979660</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7757,7 +7757,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129627679</v>
+        <v>129627769</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602740</v>
+        <v>602761</v>
       </c>
       <c r="R72" t="n">
-        <v>6979774</v>
+        <v>6979565</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7859,7 +7859,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129627676</v>
+        <v>129627679</v>
       </c>
       <c r="B73" t="n">
         <v>57736</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602825</v>
+        <v>602740</v>
       </c>
       <c r="R73" t="n">
-        <v>6979660</v>
+        <v>6979774</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4329,10 +4329,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627695</v>
+        <v>129627778</v>
       </c>
       <c r="B38" t="n">
-        <v>88998</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,21 +4340,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602860</v>
+        <v>602935</v>
       </c>
       <c r="R38" t="n">
-        <v>6979447</v>
+        <v>6979389</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627778</v>
+        <v>129627695</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>88998</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4437,21 +4437,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602935</v>
+        <v>602860</v>
       </c>
       <c r="R39" t="n">
-        <v>6979389</v>
+        <v>6979447</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627772</v>
+        <v>129627693</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>78838</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,21 +4825,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602908</v>
+        <v>602722</v>
       </c>
       <c r="R43" t="n">
-        <v>6979328</v>
+        <v>6979623</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627693</v>
+        <v>129627772</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4922,21 +4922,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602722</v>
+        <v>602908</v>
       </c>
       <c r="R44" t="n">
-        <v>6979623</v>
+        <v>6979328</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5312,7 +5312,7 @@
         <v>129627765</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129627686</v>
+        <v>129627764</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>602797</v>
+        <v>602916</v>
       </c>
       <c r="R49" t="n">
-        <v>6979572</v>
+        <v>6979371</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5513,10 +5513,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627764</v>
+        <v>129627686</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602916</v>
+        <v>602797</v>
       </c>
       <c r="R50" t="n">
-        <v>6979371</v>
+        <v>6979572</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5618,7 +5618,7 @@
         <v>129627685</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>129627762</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5819,10 +5819,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129627687</v>
+        <v>129627684</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602794</v>
+        <v>602714</v>
       </c>
       <c r="R53" t="n">
-        <v>6979575</v>
+        <v>6979668</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129627684</v>
+        <v>129627687</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>602714</v>
+        <v>602794</v>
       </c>
       <c r="R54" t="n">
-        <v>6979668</v>
+        <v>6979575</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6026,7 +6026,7 @@
         <v>129627671</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>129627674</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>129627688</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>129627768</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>129627677</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129627766</v>
+        <v>129627672</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602935</v>
+        <v>602872</v>
       </c>
       <c r="R60" t="n">
-        <v>6979466</v>
+        <v>6979492</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6635,10 +6635,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129627673</v>
+        <v>129627766</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602857</v>
+        <v>602935</v>
       </c>
       <c r="R61" t="n">
-        <v>6979536</v>
+        <v>6979466</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6740,7 +6740,7 @@
         <v>129627678</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129627672</v>
+        <v>129627673</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602872</v>
+        <v>602857</v>
       </c>
       <c r="R63" t="n">
-        <v>6979492</v>
+        <v>6979536</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129627670</v>
+        <v>129627681</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602850</v>
+        <v>602787</v>
       </c>
       <c r="R64" t="n">
-        <v>6979445</v>
+        <v>6979696</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627681</v>
+        <v>129627763</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602787</v>
+        <v>602896</v>
       </c>
       <c r="R65" t="n">
-        <v>6979696</v>
+        <v>6979327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,10 +7145,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627763</v>
+        <v>129627670</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602896</v>
+        <v>602850</v>
       </c>
       <c r="R66" t="n">
-        <v>6979327</v>
+        <v>6979445</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7250,7 +7250,7 @@
         <v>129627767</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627680</v>
+        <v>129627675</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602732</v>
+        <v>602835</v>
       </c>
       <c r="R68" t="n">
-        <v>6979746</v>
+        <v>6979550</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7451,10 +7451,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627675</v>
+        <v>129627680</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602835</v>
+        <v>602732</v>
       </c>
       <c r="R69" t="n">
-        <v>6979550</v>
+        <v>6979746</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7556,7 +7556,7 @@
         <v>129627682</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>129627676</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7757,10 +7757,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129627769</v>
+        <v>129627679</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>602761</v>
+        <v>602740</v>
       </c>
       <c r="R72" t="n">
-        <v>6979565</v>
+        <v>6979774</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7859,10 +7859,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129627679</v>
+        <v>129627769</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602740</v>
+        <v>602761</v>
       </c>
       <c r="R73" t="n">
-        <v>6979774</v>
+        <v>6979565</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>129627689</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>129627771</v>
       </c>
       <c r="B30" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3650,32 +3650,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627690</v>
+        <v>129627774</v>
       </c>
       <c r="B31" t="n">
-        <v>97661</v>
+        <v>80189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3685,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602770</v>
+        <v>602748</v>
       </c>
       <c r="R31" t="n">
-        <v>6979694</v>
+        <v>6979628</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,32 +3747,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627774</v>
+        <v>129627690</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>97665</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602748</v>
+        <v>602770</v>
       </c>
       <c r="R32" t="n">
-        <v>6979628</v>
+        <v>6979694</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627691</v>
+        <v>129627780</v>
       </c>
       <c r="B33" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602779</v>
+        <v>602750</v>
       </c>
       <c r="R33" t="n">
-        <v>6979669</v>
+        <v>6979588</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627780</v>
+        <v>129627691</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602750</v>
+        <v>602779</v>
       </c>
       <c r="R34" t="n">
-        <v>6979588</v>
+        <v>6979669</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
         <v>129627779</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>129627692</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>129627667</v>
       </c>
       <c r="B37" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>129627778</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>129627695</v>
       </c>
       <c r="B39" t="n">
-        <v>88998</v>
+        <v>89001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>129627666</v>
       </c>
       <c r="B40" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>129627775</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>129627694</v>
       </c>
       <c r="B42" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>129627693</v>
       </c>
       <c r="B43" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>129627772</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>129627773</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>129627777</v>
       </c>
       <c r="B46" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>129627770</v>
       </c>
       <c r="B47" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129627764</v>
+        <v>129627686</v>
       </c>
       <c r="B49" t="n">
         <v>57737</v>
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>602916</v>
+        <v>602797</v>
       </c>
       <c r="R49" t="n">
-        <v>6979371</v>
+        <v>6979572</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5513,7 +5513,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627686</v>
+        <v>129627764</v>
       </c>
       <c r="B50" t="n">
         <v>57737</v>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602797</v>
+        <v>602916</v>
       </c>
       <c r="R50" t="n">
-        <v>6979572</v>
+        <v>6979371</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5819,7 +5819,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129627684</v>
+        <v>129627687</v>
       </c>
       <c r="B53" t="n">
         <v>57737</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602714</v>
+        <v>602794</v>
       </c>
       <c r="R53" t="n">
-        <v>6979668</v>
+        <v>6979575</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129627687</v>
+        <v>129627684</v>
       </c>
       <c r="B54" t="n">
         <v>57737</v>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>602794</v>
+        <v>602714</v>
       </c>
       <c r="R54" t="n">
-        <v>6979575</v>
+        <v>6979668</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129627672</v>
+        <v>129627678</v>
       </c>
       <c r="B60" t="n">
         <v>57737</v>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602872</v>
+        <v>602750</v>
       </c>
       <c r="R60" t="n">
-        <v>6979492</v>
+        <v>6979758</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129627678</v>
+        <v>129627673</v>
       </c>
       <c r="B62" t="n">
         <v>57737</v>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602750</v>
+        <v>602857</v>
       </c>
       <c r="R62" t="n">
-        <v>6979758</v>
+        <v>6979536</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129627673</v>
+        <v>129627672</v>
       </c>
       <c r="B63" t="n">
         <v>57737</v>
@@ -6874,10 +6874,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602857</v>
+        <v>602872</v>
       </c>
       <c r="R63" t="n">
-        <v>6979536</v>
+        <v>6979492</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129627681</v>
+        <v>129627670</v>
       </c>
       <c r="B64" t="n">
         <v>57737</v>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602787</v>
+        <v>602850</v>
       </c>
       <c r="R64" t="n">
-        <v>6979696</v>
+        <v>6979445</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7043,7 +7043,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627763</v>
+        <v>129627681</v>
       </c>
       <c r="B65" t="n">
         <v>57737</v>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602896</v>
+        <v>602787</v>
       </c>
       <c r="R65" t="n">
-        <v>6979327</v>
+        <v>6979696</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,7 +7145,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627670</v>
+        <v>129627763</v>
       </c>
       <c r="B66" t="n">
         <v>57737</v>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602850</v>
+        <v>602896</v>
       </c>
       <c r="R66" t="n">
-        <v>6979445</v>
+        <v>6979327</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7349,7 +7349,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627675</v>
+        <v>129627680</v>
       </c>
       <c r="B68" t="n">
         <v>57737</v>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602835</v>
+        <v>602732</v>
       </c>
       <c r="R68" t="n">
-        <v>6979550</v>
+        <v>6979746</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7451,7 +7451,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627680</v>
+        <v>129627675</v>
       </c>
       <c r="B69" t="n">
         <v>57737</v>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602732</v>
+        <v>602835</v>
       </c>
       <c r="R69" t="n">
-        <v>6979746</v>
+        <v>6979550</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7655,7 +7655,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129627676</v>
+        <v>129627769</v>
       </c>
       <c r="B71" t="n">
         <v>57737</v>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602825</v>
+        <v>602761</v>
       </c>
       <c r="R71" t="n">
-        <v>6979660</v>
+        <v>6979565</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7859,7 +7859,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129627769</v>
+        <v>129627676</v>
       </c>
       <c r="B73" t="n">
         <v>57737</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>602761</v>
+        <v>602825</v>
       </c>
       <c r="R73" t="n">
-        <v>6979565</v>
+        <v>6979660</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -4620,10 +4620,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627775</v>
+        <v>129627694</v>
       </c>
       <c r="B41" t="n">
-        <v>80189</v>
+        <v>91616</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4631,21 +4631,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602854</v>
+        <v>602905</v>
       </c>
       <c r="R41" t="n">
-        <v>6979675</v>
+        <v>6979425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627694</v>
+        <v>129627775</v>
       </c>
       <c r="B42" t="n">
-        <v>91616</v>
+        <v>80189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602905</v>
+        <v>602854</v>
       </c>
       <c r="R42" t="n">
-        <v>6979425</v>
+        <v>6979675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56051928</v>
+        <v>128900356</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brotjärnarna, Mpd</t>
+          <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602691.9477760415</v>
+        <v>602819</v>
       </c>
       <c r="R2" t="n">
-        <v>6979583.4223249</v>
+        <v>6979627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,44 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # högstubbe gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56051927</v>
+        <v>128900321</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,38 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brotjärnarna, Mpd</t>
+          <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602875</v>
+        <v>602666</v>
       </c>
       <c r="R3" t="n">
-        <v>6979492</v>
+        <v>6979501</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,46 +854,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # tall</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56051926</v>
+        <v>128900325</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,38 +899,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brotjärnarna, Mpd</t>
+          <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602846.3871307813</v>
+        <v>602673</v>
       </c>
       <c r="R4" t="n">
-        <v>6979461.587130418</v>
+        <v>6979482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,41 +970,44 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>sofia nordin</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128900358</v>
+        <v>128900329</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>92205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,34 +1015,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602790</v>
+        <v>602681</v>
       </c>
       <c r="R5" t="n">
-        <v>6979633</v>
+        <v>6979457</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1149,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128900352</v>
+        <v>129627695</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602930</v>
+        <v>602860</v>
       </c>
       <c r="R6" t="n">
-        <v>6979456</v>
+        <v>6979447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,22 +1190,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128900331</v>
+        <v>56051926</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,34 +1213,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärnsberget, Mpd</t>
+          <t>Brotjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602765</v>
+        <v>602846</v>
       </c>
       <c r="R7" t="n">
-        <v>6979444</v>
+        <v>6979462</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,12 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,48 +1287,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128900341</v>
+        <v>128900348</v>
       </c>
       <c r="B8" t="n">
-        <v>91556</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602855</v>
+        <v>602903</v>
       </c>
       <c r="R8" t="n">
-        <v>6979435</v>
+        <v>6979432</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,56 +1413,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900327</v>
+        <v>129627667</v>
       </c>
       <c r="B9" t="n">
-        <v>91836</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602681</v>
+        <v>602690</v>
       </c>
       <c r="R9" t="n">
-        <v>6979457</v>
+        <v>6979583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,12 +1478,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,71 +1492,50 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900369</v>
+        <v>128900350</v>
       </c>
       <c r="B10" t="n">
-        <v>83012</v>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602622</v>
+        <v>602903</v>
       </c>
       <c r="R10" t="n">
-        <v>6979655</v>
+        <v>6979432</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,32 +1607,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900373</v>
+        <v>129627694</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>602610</v>
+        <v>602905</v>
       </c>
       <c r="R11" t="n">
-        <v>6979543</v>
+        <v>6979425</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,12 +1672,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,44 +1692,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900354</v>
+        <v>128900341</v>
       </c>
       <c r="B12" t="n">
-        <v>82878</v>
+        <v>91920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602883</v>
+        <v>602855</v>
       </c>
       <c r="R12" t="n">
-        <v>6979584</v>
+        <v>6979435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1783,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1861,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900364</v>
+        <v>128900354</v>
       </c>
       <c r="B13" t="n">
-        <v>83012</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,21 +1812,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602698</v>
+        <v>602883</v>
       </c>
       <c r="R13" t="n">
-        <v>6979648</v>
+        <v>6979584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,6 +1880,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1958,45 +1899,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900335</v>
+        <v>128900327</v>
       </c>
       <c r="B14" t="n">
-        <v>80184</v>
+        <v>92201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>1964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602837</v>
+        <v>602681</v>
       </c>
       <c r="R14" t="n">
-        <v>6979499</v>
+        <v>6979457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,8 +1989,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2055,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128900366</v>
+        <v>128900346</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>91893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2090,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602670</v>
+        <v>602871</v>
       </c>
       <c r="R15" t="n">
-        <v>6979642</v>
+        <v>6979361</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,32 +2125,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128900371</v>
+        <v>129627666</v>
       </c>
       <c r="B16" t="n">
-        <v>83012</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602623</v>
+        <v>602670</v>
       </c>
       <c r="R16" t="n">
-        <v>6979560</v>
+        <v>6979481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2217,12 +2190,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,60 +2210,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128900329</v>
+        <v>128900331</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602681</v>
+        <v>602765</v>
       </c>
       <c r="R17" t="n">
-        <v>6979457</v>
+        <v>6979444</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,7 +2301,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2350,48 +2319,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128900325</v>
+        <v>128900352</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602673</v>
+        <v>602930</v>
       </c>
       <c r="R18" t="n">
-        <v>6979482</v>
+        <v>6979456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,24 +2398,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2466,32 +2416,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128900348</v>
+        <v>128900360</v>
       </c>
       <c r="B19" t="n">
-        <v>91545</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2501,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602903</v>
+        <v>602724</v>
       </c>
       <c r="R19" t="n">
-        <v>6979432</v>
+        <v>6979757</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,32 +2513,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128900362</v>
+        <v>128900366</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602738</v>
+        <v>602670</v>
       </c>
       <c r="R20" t="n">
-        <v>6979736</v>
+        <v>6979642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,48 +2610,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128900321</v>
+        <v>128900373</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kroktjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602666</v>
+        <v>602610</v>
       </c>
       <c r="R21" t="n">
-        <v>6979501</v>
+        <v>6979543</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,24 +2689,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2776,30 +2707,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128900343</v>
+        <v>129627778</v>
       </c>
       <c r="B22" t="n">
-        <v>91565</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2807,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602836</v>
+        <v>602935</v>
       </c>
       <c r="R22" t="n">
-        <v>6979368</v>
+        <v>6979389</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,12 +2772,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2857,44 +2792,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128900350</v>
+        <v>129627779</v>
       </c>
       <c r="B23" t="n">
-        <v>91559</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2904,10 +2839,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>602903</v>
+        <v>602869</v>
       </c>
       <c r="R23" t="n">
-        <v>6979432</v>
+        <v>6979601</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,12 +2869,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,22 +2889,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128900356</v>
+        <v>129627780</v>
       </c>
       <c r="B24" t="n">
-        <v>91818</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2977,21 +2912,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +2936,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>602819</v>
+        <v>602750</v>
       </c>
       <c r="R24" t="n">
-        <v>6979627</v>
+        <v>6979588</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +2966,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3051,12 +2986,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Clara Lerbro</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3066,7 +3001,7 @@
         <v>128900344</v>
       </c>
       <c r="B25" t="n">
-        <v>83012</v>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,32 +3095,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128900346</v>
+        <v>128900364</v>
       </c>
       <c r="B26" t="n">
-        <v>91529</v>
+        <v>83307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4660</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3195,10 +3130,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>602871</v>
+        <v>602698</v>
       </c>
       <c r="R26" t="n">
-        <v>6979361</v>
+        <v>6979648</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3257,10 +3192,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128900360</v>
+        <v>128900369</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>83307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,21 +3203,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3292,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>602724</v>
+        <v>602622</v>
       </c>
       <c r="R27" t="n">
-        <v>6979757</v>
+        <v>6979655</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,10 +3289,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128900339</v>
+        <v>128900371</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3365,21 +3300,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3389,10 +3324,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>602837</v>
+        <v>602623</v>
       </c>
       <c r="R28" t="n">
-        <v>6979499</v>
+        <v>6979560</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3451,10 +3386,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129627689</v>
+        <v>129627693</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3462,21 +3397,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3486,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>602773</v>
+        <v>602722</v>
       </c>
       <c r="R29" t="n">
-        <v>6979714</v>
+        <v>6979623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3522,11 +3457,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3553,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129627771</v>
+        <v>128900362</v>
       </c>
       <c r="B30" t="n">
-        <v>97668</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3588,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>602782</v>
+        <v>602738</v>
       </c>
       <c r="R30" t="n">
-        <v>6979624</v>
+        <v>6979736</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3618,12 +3548,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3638,22 +3568,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129627774</v>
+        <v>128900339</v>
       </c>
       <c r="B31" t="n">
-        <v>80192</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3685,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>602748</v>
+        <v>602837</v>
       </c>
       <c r="R31" t="n">
-        <v>6979628</v>
+        <v>6979499</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3715,12 +3645,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3735,44 +3665,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129627690</v>
+        <v>128900358</v>
       </c>
       <c r="B32" t="n">
-        <v>97668</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3782,10 +3712,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>602770</v>
+        <v>602790</v>
       </c>
       <c r="R32" t="n">
-        <v>6979694</v>
+        <v>6979633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3812,12 +3742,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3832,22 +3762,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129627780</v>
+        <v>129627691</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,21 +3785,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3809,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>602750</v>
+        <v>602779</v>
       </c>
       <c r="R33" t="n">
-        <v>6979588</v>
+        <v>6979669</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3871,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129627691</v>
+        <v>129627692</v>
       </c>
       <c r="B34" t="n">
-        <v>80192</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3976,10 +3906,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>602779</v>
+        <v>602707</v>
       </c>
       <c r="R34" t="n">
-        <v>6979669</v>
+        <v>6979618</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,10 +3968,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129627667</v>
+        <v>129627772</v>
       </c>
       <c r="B35" t="n">
-        <v>91605</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +3979,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4003,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>602690</v>
+        <v>602908</v>
       </c>
       <c r="R35" t="n">
-        <v>6979583</v>
+        <v>6979328</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4135,10 +4065,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129627779</v>
+        <v>129627773</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4146,21 +4076,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4100,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>602869</v>
+        <v>602909</v>
       </c>
       <c r="R36" t="n">
-        <v>6979601</v>
+        <v>6979335</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,10 +4162,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129627692</v>
+        <v>129627774</v>
       </c>
       <c r="B37" t="n">
-        <v>80192</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,10 +4197,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>602707</v>
+        <v>602748</v>
       </c>
       <c r="R37" t="n">
-        <v>6979618</v>
+        <v>6979628</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,10 +4259,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129627695</v>
+        <v>129627775</v>
       </c>
       <c r="B38" t="n">
-        <v>89004</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,21 +4270,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4364,10 +4294,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>602860</v>
+        <v>602854</v>
       </c>
       <c r="R38" t="n">
-        <v>6979447</v>
+        <v>6979675</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4426,27 +4356,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129627778</v>
+        <v>128900335</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4461,10 +4391,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>602935</v>
+        <v>602837</v>
       </c>
       <c r="R39" t="n">
-        <v>6979389</v>
+        <v>6979499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4491,12 +4421,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4511,22 +4441,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Clara Lerbro</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129627666</v>
+        <v>129627689</v>
       </c>
       <c r="B40" t="n">
-        <v>91569</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4534,21 +4464,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4558,10 +4488,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>602670</v>
+        <v>602773</v>
       </c>
       <c r="R40" t="n">
-        <v>6979481</v>
+        <v>6979714</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4594,6 +4524,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4620,10 +4555,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129627694</v>
+        <v>56051927</v>
       </c>
       <c r="B41" t="n">
-        <v>91619</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4631,34 +4566,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kroktjärnsberget, Mpd</t>
+          <t>Brotjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>602905</v>
+        <v>602875</v>
       </c>
       <c r="R41" t="n">
-        <v>6979425</v>
+        <v>6979492</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4685,12 +4624,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4701,26 +4640,39 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tall</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>sofia nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129627775</v>
+        <v>129627670</v>
       </c>
       <c r="B42" t="n">
-        <v>80192</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4728,21 +4680,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4752,10 +4704,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>602854</v>
+        <v>602850</v>
       </c>
       <c r="R42" t="n">
-        <v>6979675</v>
+        <v>6979445</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4788,6 +4740,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4814,10 +4771,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129627693</v>
+        <v>129627671</v>
       </c>
       <c r="B43" t="n">
-        <v>78844</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4825,21 +4782,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4849,10 +4806,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>602722</v>
+        <v>602903</v>
       </c>
       <c r="R43" t="n">
-        <v>6979623</v>
+        <v>6979431</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4885,6 +4842,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4911,10 +4873,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129627772</v>
+        <v>129627672</v>
       </c>
       <c r="B44" t="n">
-        <v>80192</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4922,21 +4884,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4946,10 +4908,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>602908</v>
+        <v>602872</v>
       </c>
       <c r="R44" t="n">
-        <v>6979328</v>
+        <v>6979492</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4982,6 +4944,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5008,10 +4975,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129627773</v>
+        <v>129627673</v>
       </c>
       <c r="B45" t="n">
-        <v>80192</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5019,21 +4986,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5043,10 +5010,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>602909</v>
+        <v>602857</v>
       </c>
       <c r="R45" t="n">
-        <v>6979335</v>
+        <v>6979536</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5079,6 +5046,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5105,32 +5077,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129627777</v>
+        <v>129627674</v>
       </c>
       <c r="B46" t="n">
-        <v>98797</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5140,10 +5112,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>602720</v>
+        <v>602809</v>
       </c>
       <c r="R46" t="n">
-        <v>6979669</v>
+        <v>6979547</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5180,7 +5152,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>150 stycken ca</t>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5207,10 +5179,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129627770</v>
+        <v>129627675</v>
       </c>
       <c r="B47" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5218,21 +5190,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5242,10 +5214,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>602876</v>
+        <v>602835</v>
       </c>
       <c r="R47" t="n">
-        <v>6979597</v>
+        <v>6979550</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5282,7 +5254,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2 ex, övriga/lockläten läten.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5309,10 +5281,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129627765</v>
+        <v>129627676</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,10 +5316,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>602904</v>
+        <v>602825</v>
       </c>
       <c r="R48" t="n">
-        <v>6979415</v>
+        <v>6979660</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,7 +5356,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall färska spår.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5411,10 +5383,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129627686</v>
+        <v>129627677</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5446,10 +5418,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>602797</v>
+        <v>602776</v>
       </c>
       <c r="R49" t="n">
-        <v>6979572</v>
+        <v>6979680</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5513,10 +5485,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129627764</v>
+        <v>129627678</v>
       </c>
       <c r="B50" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,10 +5520,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>602916</v>
+        <v>602750</v>
       </c>
       <c r="R50" t="n">
-        <v>6979371</v>
+        <v>6979758</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5588,7 +5560,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5615,10 +5587,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129627685</v>
+        <v>129627679</v>
       </c>
       <c r="B51" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5650,10 +5622,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>602797</v>
+        <v>602740</v>
       </c>
       <c r="R51" t="n">
-        <v>6979575</v>
+        <v>6979774</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5717,10 +5689,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129627762</v>
+        <v>129627680</v>
       </c>
       <c r="B52" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5752,10 +5724,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>602818</v>
+        <v>602732</v>
       </c>
       <c r="R52" t="n">
-        <v>6979362</v>
+        <v>6979746</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5792,7 +5764,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5819,10 +5791,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129627687</v>
+        <v>129627681</v>
       </c>
       <c r="B53" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5854,10 +5826,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>602794</v>
+        <v>602787</v>
       </c>
       <c r="R53" t="n">
-        <v>6979575</v>
+        <v>6979696</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5921,10 +5893,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129627684</v>
+        <v>129627682</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,10 +5928,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>602714</v>
+        <v>602720</v>
       </c>
       <c r="R54" t="n">
-        <v>6979668</v>
+        <v>6979665</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6023,10 +5995,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129627671</v>
+        <v>129627684</v>
       </c>
       <c r="B55" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,10 +6030,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>602903</v>
+        <v>602714</v>
       </c>
       <c r="R55" t="n">
-        <v>6979431</v>
+        <v>6979668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6125,10 +6097,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129627674</v>
+        <v>129627685</v>
       </c>
       <c r="B56" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6160,10 +6132,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>602809</v>
+        <v>602797</v>
       </c>
       <c r="R56" t="n">
-        <v>6979547</v>
+        <v>6979575</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6200,7 +6172,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1 ex födosökande</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,10 +6199,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129627688</v>
+        <v>129627686</v>
       </c>
       <c r="B57" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6262,10 +6234,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>602759</v>
+        <v>602797</v>
       </c>
       <c r="R57" t="n">
-        <v>6979557</v>
+        <v>6979572</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6329,10 +6301,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129627768</v>
+        <v>129627687</v>
       </c>
       <c r="B58" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6364,10 +6336,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>602780</v>
+        <v>602794</v>
       </c>
       <c r="R58" t="n">
-        <v>6979618</v>
+        <v>6979575</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6404,7 +6376,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett, färska spår på tall.</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6431,10 +6403,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129627677</v>
+        <v>129627688</v>
       </c>
       <c r="B59" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6466,10 +6438,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>602776</v>
+        <v>602759</v>
       </c>
       <c r="R59" t="n">
-        <v>6979680</v>
+        <v>6979557</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6533,10 +6505,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129627766</v>
+        <v>129627762</v>
       </c>
       <c r="B60" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6568,10 +6540,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>602935</v>
+        <v>602818</v>
       </c>
       <c r="R60" t="n">
-        <v>6979466</v>
+        <v>6979362</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,7 +6580,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>1 ex observerad i gran, puttsar fjädrarna i regnet.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6635,10 +6607,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129627673</v>
+        <v>129627763</v>
       </c>
       <c r="B61" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6670,10 +6642,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>602857</v>
+        <v>602896</v>
       </c>
       <c r="R61" t="n">
-        <v>6979536</v>
+        <v>6979327</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,7 +6682,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,10 +6709,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129627678</v>
+        <v>129627764</v>
       </c>
       <c r="B62" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6772,10 +6744,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>602750</v>
+        <v>602916</v>
       </c>
       <c r="R62" t="n">
-        <v>6979758</v>
+        <v>6979371</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6812,7 +6784,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6839,10 +6811,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129627672</v>
+        <v>129627765</v>
       </c>
       <c r="B63" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6874,10 +6846,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>602872</v>
+        <v>602904</v>
       </c>
       <c r="R63" t="n">
-        <v>6979492</v>
+        <v>6979415</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,7 +6886,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall färska spår.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,10 +6913,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129627670</v>
+        <v>129627766</v>
       </c>
       <c r="B64" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6976,10 +6948,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>602850</v>
+        <v>602935</v>
       </c>
       <c r="R64" t="n">
-        <v>6979445</v>
+        <v>6979466</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7016,7 +6988,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7043,10 +7015,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129627681</v>
+        <v>129627767</v>
       </c>
       <c r="B65" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7078,10 +7050,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>602787</v>
+        <v>602703</v>
       </c>
       <c r="R65" t="n">
-        <v>6979696</v>
+        <v>6979746</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,7 +7090,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7145,10 +7117,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129627763</v>
+        <v>129627768</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7180,10 +7152,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>602896</v>
+        <v>602780</v>
       </c>
       <c r="R66" t="n">
-        <v>6979327</v>
+        <v>6979618</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7220,7 +7192,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall. Färska spår.</t>
+          <t>Ringhack av tretåig hackspett, färska spår på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7247,10 +7219,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129627767</v>
+        <v>129627769</v>
       </c>
       <c r="B67" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,10 +7254,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>602703</v>
+        <v>602761</v>
       </c>
       <c r="R67" t="n">
-        <v>6979746</v>
+        <v>6979565</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7322,7 +7294,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på tall, färska spår.</t>
+          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7349,10 +7321,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129627680</v>
+        <v>129627770</v>
       </c>
       <c r="B68" t="n">
-        <v>57741</v>
+        <v>58114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7360,21 +7332,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7384,10 +7356,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>602732</v>
+        <v>602876</v>
       </c>
       <c r="R68" t="n">
-        <v>6979746</v>
+        <v>6979597</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7424,7 +7396,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>2 ex, övriga/lockläten läten.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7451,32 +7423,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129627675</v>
+        <v>129627777</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7486,10 +7458,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>602835</v>
+        <v>602720</v>
       </c>
       <c r="R69" t="n">
-        <v>6979550</v>
+        <v>6979669</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7526,7 +7498,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>150 stycken ca</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7553,32 +7525,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129627682</v>
+        <v>129627690</v>
       </c>
       <c r="B70" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7588,10 +7560,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>602720</v>
+        <v>602770</v>
       </c>
       <c r="R70" t="n">
-        <v>6979665</v>
+        <v>6979694</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7624,11 +7596,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7655,32 +7622,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129627769</v>
+        <v>129627771</v>
       </c>
       <c r="B71" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7690,10 +7657,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>602761</v>
+        <v>602782</v>
       </c>
       <c r="R71" t="n">
-        <v>6979565</v>
+        <v>6979624</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7728,11 +7695,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringack av tretåig hackspett på tall. Färska spår.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7754,210 +7716,6 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>129627679</v>
-      </c>
-      <c r="B72" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Kroktjärnsberget, Mpd</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>602740</v>
-      </c>
-      <c r="R72" t="n">
-        <v>6979774</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Liden</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>129627676</v>
-      </c>
-      <c r="B73" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Kroktjärnsberget, Mpd</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>602825</v>
-      </c>
-      <c r="R73" t="n">
-        <v>6979660</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Liden</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51286-2025 artfynd.xlsx
+++ b/artfynd/A 51286-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900356</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900321</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900329</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627695</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56051926</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900348</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627667</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900350</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627694</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900341</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900354</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900327</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900346</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627666</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900331</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900352</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900360</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2607,6 +2702,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900366</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2704,6 +2804,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900373</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2801,6 +2906,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627778</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2898,6 +3008,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627779</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627780</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3092,6 +3212,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900344</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3189,6 +3314,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900364</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3286,6 +3416,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900369</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3383,6 +3518,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900371</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3480,6 +3620,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627693</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3577,6 +3722,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900362</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3674,6 +3824,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900339</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3771,6 +3926,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900358</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3868,6 +4028,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627691</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3965,6 +4130,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627692</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4062,6 +4232,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627772</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4159,6 +4334,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627773</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4256,6 +4436,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627774</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4353,6 +4538,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627775</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4450,6 +4640,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128900335</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4552,6 +4747,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627689</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4666,6 +4866,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56051927</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4768,6 +4973,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627670</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4870,6 +5080,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627671</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4972,6 +5187,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627672</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5074,6 +5294,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627673</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5176,6 +5401,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627674</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5278,6 +5508,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627675</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5380,6 +5615,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627676</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5482,6 +5722,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627677</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5584,6 +5829,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627678</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5686,6 +5936,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627679</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5788,6 +6043,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627680</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5890,6 +6150,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627681</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5992,6 +6257,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627682</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6094,6 +6364,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627684</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6196,6 +6471,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627685</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6298,6 +6578,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627686</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6400,6 +6685,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627687</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6502,6 +6792,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627688</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6604,6 +6899,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627762</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6706,6 +7006,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627763</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6808,6 +7113,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627764</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6910,6 +7220,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627765</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7012,6 +7327,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627766</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7114,6 +7434,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627767</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7216,6 +7541,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627768</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7318,6 +7648,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627769</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7420,6 +7755,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627770</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7522,6 +7862,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627777</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7619,6 +7964,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627690</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7716,8 +8066,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129627771</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>